--- a/database/Equipment_Register.xlsx
+++ b/database/Equipment_Register.xlsx
@@ -10,12 +10,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="416">
   <si>
     <t xml:space="preserve">WORKSHOP EQUIPMENT REGISTER — 21 OCTOBER 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated 21/10/2026 11:29 by WMSv2 Recovery  •  116 assets  •  Availability = (operating hours − downtime) ÷ operating hours</t>
+    <t xml:space="preserve">Generated 21/10/2026 12:07 by WMSv2 Recovery  •  116 assets  •  Availability = (operating hours − downtime) ÷ operating hours</t>
   </si>
   <si>
     <t xml:space="preserve">ID</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">SY500H</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-EX-001</t>
+    <t xml:space="preserve">SY048CE0007K8</t>
   </si>
   <si>
     <t xml:space="preserve">6WG1</t>
@@ -162,7 +162,7 @@
     <t xml:space="preserve">XE500DK</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-EX-002</t>
+    <t xml:space="preserve">XCGA500APKA03918</t>
   </si>
   <si>
     <t xml:space="preserve">QSM11</t>
@@ -180,13 +180,13 @@
     <t xml:space="preserve">C-HV-EX 003</t>
   </si>
   <si>
-    <t xml:space="preserve">CATERPILAR</t>
+    <t xml:space="preserve">CATERPILLAR</t>
   </si>
   <si>
     <t xml:space="preserve">390 FL</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-EX-003</t>
+    <t xml:space="preserve">CAT0390FTGAY20127</t>
   </si>
   <si>
     <t xml:space="preserve">C18</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">XE950</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-EX-004</t>
+    <t xml:space="preserve">XUG09503PSWA03818</t>
   </si>
   <si>
     <t xml:space="preserve">QSK19</t>
@@ -216,13 +216,13 @@
     <t xml:space="preserve">C-HV-EX 005</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-EX-005</t>
+    <t xml:space="preserve">XUG09503HSWA03828</t>
   </si>
   <si>
     <t xml:space="preserve">Bucket Worn out</t>
   </si>
   <si>
-    <t xml:space="preserve">EX 006</t>
+    <t xml:space="preserve">C-HV-EX 006</t>
   </si>
   <si>
     <t xml:space="preserve">XE500</t>
@@ -240,13 +240,10 @@
     <t xml:space="preserve">Dozer</t>
   </si>
   <si>
-    <t xml:space="preserve">DOZER D8R</t>
-  </si>
-  <si>
     <t xml:space="preserve">D8R</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-DZ-001</t>
+    <t xml:space="preserve">GN0003844</t>
   </si>
   <si>
     <t xml:space="preserve">3406C</t>
@@ -258,13 +255,13 @@
     <t xml:space="preserve">C-HV-DZ 002</t>
   </si>
   <si>
-    <t xml:space="preserve">DOZER LIUGONG</t>
+    <t xml:space="preserve">LIUGONG</t>
   </si>
   <si>
     <t xml:space="preserve">CLG B230</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-DZ-002</t>
+    <t xml:space="preserve">LGCB230ZHRCO12870</t>
   </si>
   <si>
     <t xml:space="preserve">NT855C280S20</t>
@@ -276,7 +273,7 @@
     <t xml:space="preserve">C-HV-DZ 003</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-DZ-003</t>
+    <t xml:space="preserve">LGCB230ZCRC012829</t>
   </si>
   <si>
     <t xml:space="preserve">Transmission problem</t>
@@ -285,13 +282,10 @@
     <t xml:space="preserve">C-HV-DZ 004</t>
   </si>
   <si>
-    <t xml:space="preserve">XCMG DOZER</t>
-  </si>
-  <si>
     <t xml:space="preserve">D 260</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-DZ-004</t>
+    <t xml:space="preserve">XUG260T3CRDK00066</t>
   </si>
   <si>
     <t xml:space="preserve">SC9DF270G3</t>
@@ -303,7 +297,7 @@
     <t xml:space="preserve">C-HV-DZ 005</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-DZ-005</t>
+    <t xml:space="preserve">XUG260T3TRDK00067</t>
   </si>
   <si>
     <t xml:space="preserve">Steering system and Joystick issue</t>
@@ -321,7 +315,7 @@
     <t xml:space="preserve">C-HV-DZ 007</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-DZ-007</t>
+    <t xml:space="preserve">XUG360T2ASDK00063</t>
   </si>
   <si>
     <t xml:space="preserve">C-HE-ADT 001</t>
@@ -339,19 +333,19 @@
     <t xml:space="preserve">C-HE-ADT 002</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-ADT-002</t>
+    <t xml:space="preserve">CAT00745E3F602018</t>
   </si>
   <si>
     <t xml:space="preserve">C-HE-ADT 003</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-ADT-003</t>
+    <t xml:space="preserve">CAT00745T3F602023</t>
   </si>
   <si>
     <t xml:space="preserve">C-HE-ADT 004</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-ADT-004</t>
+    <t xml:space="preserve">CAT00745T3F601163</t>
   </si>
   <si>
     <t xml:space="preserve">Cabin Pin Worn out</t>
@@ -360,7 +354,7 @@
     <t xml:space="preserve">C-HE-ADT 005</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-ADT-005</t>
+    <t xml:space="preserve">CAT00745P3F601195</t>
   </si>
   <si>
     <t xml:space="preserve">MINING</t>
@@ -369,25 +363,25 @@
     <t xml:space="preserve">C-HE-ADT 006</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-ADT-006</t>
+    <t xml:space="preserve">CAT00745C3F601193</t>
   </si>
   <si>
     <t xml:space="preserve">Engine no start</t>
   </si>
   <si>
-    <t xml:space="preserve">C-HEADT 007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SN-ADT-007</t>
+    <t xml:space="preserve">C-HE-ADT 007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT00745P3F601164</t>
   </si>
   <si>
     <t xml:space="preserve">Differential problem</t>
   </si>
   <si>
-    <t xml:space="preserve">C-HEADT 008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SN-ADT-008</t>
+    <t xml:space="preserve">C-HE-ADT 008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT00745V3F601199</t>
   </si>
   <si>
     <t xml:space="preserve">C-HE-ADT 009</t>
@@ -396,7 +390,7 @@
     <t xml:space="preserve">XDA45</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-ADT-009</t>
+    <t xml:space="preserve">XUG00456VRWB00458</t>
   </si>
   <si>
     <t xml:space="preserve">Benz OM502</t>
@@ -405,19 +399,19 @@
     <t xml:space="preserve">C-HE-ADT 010</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-ADT-010</t>
+    <t xml:space="preserve">XUG00456KRWB00438</t>
   </si>
   <si>
     <t xml:space="preserve">C-HE-ADT 011</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-ADT-011</t>
+    <t xml:space="preserve">XUG00456ARWB00428</t>
   </si>
   <si>
     <t xml:space="preserve">C-HE-ADT 012</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-ADT-012</t>
+    <t xml:space="preserve">XUG00456PRWB00468</t>
   </si>
   <si>
     <t xml:space="preserve">Turbo failure</t>
@@ -426,7 +420,7 @@
     <t xml:space="preserve">C-HE-ADT 013</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-ADT-013</t>
+    <t xml:space="preserve">XUG00456ERWB00448</t>
   </si>
   <si>
     <t xml:space="preserve">Flat tire - Fixed</t>
@@ -435,7 +429,7 @@
     <t xml:space="preserve">C-HE-ADT 014</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-ADT-014</t>
+    <t xml:space="preserve">XUG00456VRWB00508</t>
   </si>
   <si>
     <t xml:space="preserve">4000h service done</t>
@@ -444,13 +438,13 @@
     <t xml:space="preserve">C-HE-ADT 015</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-ADT-015</t>
+    <t xml:space="preserve">XUG00456CRWB00488</t>
   </si>
   <si>
     <t xml:space="preserve">C-HE-ADT 016</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-ADT-016</t>
+    <t xml:space="preserve">XUG00456TRWB00498</t>
   </si>
   <si>
     <t xml:space="preserve">Radiator Leakage</t>
@@ -459,13 +453,13 @@
     <t xml:space="preserve">C-HE-ADT 017</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-ADT-017</t>
+    <t xml:space="preserve">XUG00456PRWB00518</t>
   </si>
   <si>
     <t xml:space="preserve">C-HE-ADT 018</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-ADT-018</t>
+    <t xml:space="preserve">XUG00456HRWB00478</t>
   </si>
   <si>
     <t xml:space="preserve">C-HE-GR 001</t>
@@ -480,7 +474,7 @@
     <t xml:space="preserve">GR2405T</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-GR-001</t>
+    <t xml:space="preserve">XUG240T3ARDB00020</t>
   </si>
   <si>
     <t xml:space="preserve">Injectors issue</t>
@@ -489,7 +483,7 @@
     <t xml:space="preserve">C-HE-GR 002</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-GR-002</t>
+    <t xml:space="preserve">XUG240T3ARDB00021</t>
   </si>
   <si>
     <t xml:space="preserve">Engine and Transmission issue</t>
@@ -510,7 +504,7 @@
     <t xml:space="preserve">ZZ1257N4647B1R</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-DB-001</t>
+    <t xml:space="preserve">LZZ5BLMFXRN296483</t>
   </si>
   <si>
     <t xml:space="preserve">TTB PAMAO</t>
@@ -522,7 +516,7 @@
     <t xml:space="preserve">ZZ1168G4525C1</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-DB-002</t>
+    <t xml:space="preserve">LEZDD2CC1PF112146</t>
   </si>
   <si>
     <t xml:space="preserve">Pipe/line leakage</t>
@@ -534,7 +528,7 @@
     <t xml:space="preserve">BEIBEN</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-DB-003</t>
+    <t xml:space="preserve">LBZF46GA5PA004464</t>
   </si>
   <si>
     <t xml:space="preserve">C-HV-WB 001</t>
@@ -543,13 +537,13 @@
     <t xml:space="preserve">CNHTC</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-WB-001</t>
+    <t xml:space="preserve">LZZ5BLMF5RN290008</t>
   </si>
   <si>
     <t xml:space="preserve">C-HV-WB 002</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-WB-002</t>
+    <t xml:space="preserve">LBZF56KA8PA004463</t>
   </si>
   <si>
     <t xml:space="preserve">WP10.380E32</t>
@@ -570,7 +564,7 @@
     <t xml:space="preserve">PRD BH 15 100M</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-RIG-001</t>
+    <t xml:space="preserve">PRD252605BH150010</t>
   </si>
   <si>
     <t xml:space="preserve">IKAMVA</t>
@@ -579,7 +573,7 @@
     <t xml:space="preserve">C-AML-RIG002</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-RIG-002</t>
+    <t xml:space="preserve">PRD252604BH150009</t>
   </si>
   <si>
     <t xml:space="preserve">C-AML-RIG003</t>
@@ -591,7 +585,7 @@
     <t xml:space="preserve">EX210LC-5G</t>
   </si>
   <si>
-    <t xml:space="preserve">SN-RIG-003</t>
+    <t xml:space="preserve">THEDJLL2L00021947</t>
   </si>
   <si>
     <t xml:space="preserve">C-AML-COMP001</t>
@@ -762,10 +756,7 @@
     <t xml:space="preserve">Concrete Mixer</t>
   </si>
   <si>
-    <t xml:space="preserve">CONCRETE MIXER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZZ1257N3847B1</t>
+    <t xml:space="preserve">CONCRETE MIXER (ZZ1257N3847B1)</t>
   </si>
   <si>
     <t xml:space="preserve">OPERATIONS</t>
@@ -792,10 +783,10 @@
     <t xml:space="preserve">Light Vehicle</t>
   </si>
   <si>
-    <t xml:space="preserve">TOYOTA LANDCRUSER PICK UP DOUBLE CABIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HZJ79L-DKMRS</t>
+    <t xml:space="preserve">TOYOTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAND CRUISER PICKUP DC (HZJ79L-DKMRS)</t>
   </si>
   <si>
     <t xml:space="preserve">1HZ 4200CC DIESEL 4164ml</t>
@@ -807,10 +798,7 @@
     <t xml:space="preserve">C-LV 002</t>
   </si>
   <si>
-    <t xml:space="preserve">TOYOTA LANCRUSER 5 DOORS HARD TOP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HZJ76L-RKMRS</t>
+    <t xml:space="preserve">LAND CRUISER 5D HARD TOP (HZJ76L-RKMRS)</t>
   </si>
   <si>
     <t xml:space="preserve">1HZ 4164ml</t>
@@ -822,7 +810,7 @@
     <t xml:space="preserve">C-LV 003</t>
   </si>
   <si>
-    <t xml:space="preserve">TOYOTA LC</t>
+    <t xml:space="preserve">LAND CRUISER PICKUP DC</t>
   </si>
   <si>
     <t xml:space="preserve">PROCUREMENT MANAGER</t>
@@ -831,10 +819,10 @@
     <t xml:space="preserve">C-LV 004</t>
   </si>
   <si>
-    <t xml:space="preserve">GWM PICK UP DOUBLE CABIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC1030QS71C</t>
+    <t xml:space="preserve">GWM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PICKUP DOUBLE CABIN (CC1030QS71C)</t>
   </si>
   <si>
     <t xml:space="preserve">GW4D20M</t>
@@ -861,7 +849,7 @@
     <t xml:space="preserve">C-LV 008</t>
   </si>
   <si>
-    <t xml:space="preserve">TOYOTA LANDCRUSER HARD TOP</t>
+    <t xml:space="preserve">LAND CRUISER HARD TOP</t>
   </si>
   <si>
     <t xml:space="preserve">SAFETY MANAGER</t>
@@ -876,7 +864,7 @@
     <t xml:space="preserve">C-LV 010</t>
   </si>
   <si>
-    <t xml:space="preserve">HZJ78L-RJMRS</t>
+    <t xml:space="preserve">LAND CRUISER HARD TOP (HZJ78L-RJMRS)</t>
   </si>
   <si>
     <t xml:space="preserve">PRODUCTION (Operation)</t>
@@ -906,10 +894,7 @@
     <t xml:space="preserve">C-LV 016</t>
   </si>
   <si>
-    <t xml:space="preserve">TOYOTA HILUX PICK UP DOUBLE CABIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GUN125L-DTFSXN</t>
+    <t xml:space="preserve">HILUX PICKUP DC (GUN125L-DTFSXN)</t>
   </si>
   <si>
     <t xml:space="preserve">2GDFT</t>
@@ -930,7 +915,7 @@
     <t xml:space="preserve">C-LV 019</t>
   </si>
   <si>
-    <t xml:space="preserve">GUN125L-DTFLX</t>
+    <t xml:space="preserve">HILUX PICKUP DC (GUN125L-DTFLX)</t>
   </si>
   <si>
     <t xml:space="preserve">2GD-FTV 2393ml</t>
@@ -942,13 +927,16 @@
     <t xml:space="preserve">C-LV 020</t>
   </si>
   <si>
+    <t xml:space="preserve">PICKUP DOUBLE CABIN</t>
+  </si>
+  <si>
     <t xml:space="preserve">SUPPLY CHAIN</t>
   </si>
   <si>
     <t xml:space="preserve">C-LV 021</t>
   </si>
   <si>
-    <t xml:space="preserve">CC1030QS72C</t>
+    <t xml:space="preserve">PICKUP DOUBLE CABIN (CC1030QS72C)</t>
   </si>
   <si>
     <t xml:space="preserve">255A7011949</t>
@@ -966,7 +954,7 @@
     <t xml:space="preserve">C-LV 023</t>
   </si>
   <si>
-    <t xml:space="preserve">GUN126R-DXTHXX</t>
+    <t xml:space="preserve">HILUX PICKUP DC (GUN126R-DXTHXX)</t>
   </si>
   <si>
     <t xml:space="preserve">1GDFT</t>
@@ -1089,7 +1077,7 @@
     <t xml:space="preserve">C-WP-004</t>
   </si>
   <si>
-    <t xml:space="preserve">PUMP FOR WATER BOWSER</t>
+    <t xml:space="preserve">WATER BOWSER PUMP</t>
   </si>
   <si>
     <t xml:space="preserve">C-WP-005</t>
@@ -1131,7 +1119,10 @@
     <t xml:space="preserve">GEN-002</t>
   </si>
   <si>
-    <t xml:space="preserve">GENERATOR FG WILSON P-50</t>
+    <t xml:space="preserve">FG WILSON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-50</t>
   </si>
   <si>
     <t xml:space="preserve">BANDAYI</t>
@@ -1140,9 +1131,6 @@
     <t xml:space="preserve">GEN-003</t>
   </si>
   <si>
-    <t xml:space="preserve">GENERATOR FG WILSON</t>
-  </si>
-  <si>
     <t xml:space="preserve">P-33-3</t>
   </si>
   <si>
@@ -1182,7 +1170,10 @@
     <t xml:space="preserve">Welding Machine</t>
   </si>
   <si>
-    <t xml:space="preserve">Miller Big blue x600</t>
+    <t xml:space="preserve">MILLER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIG BLUE 600X</t>
   </si>
   <si>
     <t xml:space="preserve">TOTALS</t>
@@ -1266,7 +1257,7 @@
     <t xml:space="preserve">  existing value.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Generated 21/10/2026 11:29.</t>
+    <t xml:space="preserve">• Generated 21/10/2026 12:07.</t>
   </si>
 </sst>
 </file>
@@ -2276,19 +2267,19 @@
         <v>36</v>
       </c>
       <c r="E10" t="s" s="4">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s" s="4">
         <v>76</v>
-      </c>
-      <c r="F10" t="s" s="4">
-        <v>77</v>
       </c>
       <c r="G10" t="n" s="5">
         <v>2018</v>
       </c>
       <c r="H10" t="s" s="5">
+        <v>77</v>
+      </c>
+      <c r="I10" t="s" s="4">
         <v>78</v>
-      </c>
-      <c r="I10" t="s" s="4">
-        <v>79</v>
       </c>
       <c r="J10" t="n" s="7">
         <v>21900</v>
@@ -2335,7 +2326,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="5"/>
       <c r="AD10" t="s" s="6">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AE10" t="s" s="5">
         <v>45</v>
@@ -2349,7 +2340,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="10">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s" s="4">
         <v>75</v>
@@ -2358,19 +2349,19 @@
         <v>36</v>
       </c>
       <c r="E11" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="F11" t="s" s="4">
         <v>82</v>
-      </c>
-      <c r="F11" t="s" s="4">
-        <v>83</v>
       </c>
       <c r="G11" t="n" s="5">
         <v>2019</v>
       </c>
       <c r="H11" t="s" s="5">
+        <v>83</v>
+      </c>
+      <c r="I11" t="s" s="4">
         <v>84</v>
-      </c>
-      <c r="I11" t="s" s="4">
-        <v>85</v>
       </c>
       <c r="J11" t="n" s="7">
         <v>19200</v>
@@ -2417,7 +2408,7 @@
       <c r="AB11" s="9"/>
       <c r="AC11" s="5"/>
       <c r="AD11" t="s" s="6">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AE11" t="s" s="5">
         <v>45</v>
@@ -2431,7 +2422,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="10">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s" s="4">
         <v>75</v>
@@ -2440,19 +2431,19 @@
         <v>36</v>
       </c>
       <c r="E12" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="F12" t="s" s="4">
         <v>82</v>
-      </c>
-      <c r="F12" t="s" s="4">
-        <v>83</v>
       </c>
       <c r="G12" t="n" s="5">
         <v>2020</v>
       </c>
       <c r="H12" t="s" s="5">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I12" t="s" s="4">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J12" t="n" s="7">
         <v>16700</v>
@@ -2499,7 +2490,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="5"/>
       <c r="AD12" t="s" s="6">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AE12" t="s" s="5">
         <v>45</v>
@@ -2513,7 +2504,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="10">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s" s="4">
         <v>75</v>
@@ -2522,19 +2513,19 @@
         <v>36</v>
       </c>
       <c r="E13" t="s" s="4">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s" s="4">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G13" t="n" s="5">
         <v>2020</v>
       </c>
       <c r="H13" t="s" s="5">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s" s="4">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J13" t="n" s="7">
         <v>13200</v>
@@ -2581,7 +2572,7 @@
       <c r="AB13" s="9"/>
       <c r="AC13" s="5"/>
       <c r="AD13" t="s" s="6">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AE13" t="s" s="5">
         <v>45</v>
@@ -2595,7 +2586,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="10">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s" s="4">
         <v>75</v>
@@ -2604,19 +2595,19 @@
         <v>36</v>
       </c>
       <c r="E14" t="s" s="4">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="F14" t="s" s="4">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G14" t="n" s="5">
         <v>2021</v>
       </c>
       <c r="H14" t="s" s="5">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I14" t="s" s="4">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J14" t="n" s="7">
         <v>11800</v>
@@ -2663,7 +2654,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="5"/>
       <c r="AD14" t="s" s="6">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AE14" t="s" s="5">
         <v>45</v>
@@ -2677,7 +2668,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="10">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s" s="4">
         <v>75</v>
@@ -2686,16 +2677,16 @@
         <v>36</v>
       </c>
       <c r="E15" t="s" s="4">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="F15" t="s" s="4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G15" t="n" s="5">
         <v>2021</v>
       </c>
       <c r="H15" t="s" s="5">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" t="n" s="7">
@@ -2757,7 +2748,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="10">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s" s="4">
         <v>75</v>
@@ -2766,16 +2757,16 @@
         <v>36</v>
       </c>
       <c r="E16" t="s" s="4">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="F16" t="s" s="4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G16" t="n" s="5">
         <v>2022</v>
       </c>
       <c r="H16" t="s" s="5">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" t="n" s="7">
@@ -2837,13 +2828,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="10">
+        <v>102</v>
+      </c>
+      <c r="C17" t="s" s="4">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s" s="4">
         <v>104</v>
-      </c>
-      <c r="C17" t="s" s="4">
-        <v>105</v>
-      </c>
-      <c r="D17" t="s" s="4">
-        <v>106</v>
       </c>
       <c r="E17" t="s" s="4">
         <v>56</v>
@@ -2855,7 +2846,7 @@
         <v>2019</v>
       </c>
       <c r="H17" t="s" s="5">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I17" t="s" s="4">
         <v>59</v>
@@ -2917,13 +2908,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="10">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E18" t="s" s="4">
         <v>56</v>
@@ -2935,7 +2926,7 @@
         <v>2019</v>
       </c>
       <c r="H18" t="s" s="5">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I18" t="s" s="4">
         <v>59</v>
@@ -2999,13 +2990,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="10">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C19" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s" s="4">
         <v>56</v>
@@ -3017,7 +3008,7 @@
         <v>2020</v>
       </c>
       <c r="H19" t="s" s="5">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I19" t="s" s="4">
         <v>59</v>
@@ -3081,13 +3072,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="10">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s" s="4">
         <v>56</v>
@@ -3099,7 +3090,7 @@
         <v>2020</v>
       </c>
       <c r="H20" t="s" s="5">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I20" t="s" s="4">
         <v>59</v>
@@ -3149,7 +3140,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="5"/>
       <c r="AD20" t="s" s="6">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AE20" t="s" s="5">
         <v>45</v>
@@ -3163,13 +3154,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="10">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s" s="4">
         <v>56</v>
@@ -3181,7 +3172,7 @@
         <v>2020</v>
       </c>
       <c r="H21" t="s" s="5">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I21" t="s" s="4">
         <v>59</v>
@@ -3193,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="s" s="4">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M21" t="s" s="17">
         <v>53</v>
@@ -3245,13 +3236,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="10">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s" s="4">
         <v>56</v>
@@ -3263,7 +3254,7 @@
         <v>2021</v>
       </c>
       <c r="H22" t="s" s="5">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I22" t="s" s="4">
         <v>59</v>
@@ -3275,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="s" s="4">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M22" t="s" s="18">
         <v>42</v>
@@ -3313,7 +3304,7 @@
       <c r="AB22" s="9"/>
       <c r="AC22" s="5"/>
       <c r="AD22" t="s" s="6">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AE22" t="s" s="5">
         <v>45</v>
@@ -3327,13 +3318,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="10">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s" s="4">
         <v>56</v>
@@ -3345,7 +3336,7 @@
         <v>2021</v>
       </c>
       <c r="H23" t="s" s="5">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I23" t="s" s="4">
         <v>59</v>
@@ -3395,7 +3386,7 @@
       <c r="AB23" s="9"/>
       <c r="AC23" s="5"/>
       <c r="AD23" t="s" s="6">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AE23" t="s" s="5">
         <v>45</v>
@@ -3409,13 +3400,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="10">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s" s="4">
         <v>56</v>
@@ -3427,7 +3418,7 @@
         <v>2021</v>
       </c>
       <c r="H24" t="s" s="5">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I24" t="s" s="4">
         <v>59</v>
@@ -3491,28 +3482,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="10">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F25" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G25" t="n" s="5">
         <v>2022</v>
       </c>
       <c r="H25" t="s" s="5">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I25" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J25" t="n" s="7">
         <v>9800</v>
@@ -3573,28 +3564,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="10">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C26" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F26" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G26" t="n" s="5">
         <v>2022</v>
       </c>
       <c r="H26" t="s" s="5">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I26" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J26" t="n" s="7">
         <v>8900</v>
@@ -3655,28 +3646,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="10">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C27" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E27" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F27" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G27" t="n" s="5">
         <v>2022</v>
       </c>
       <c r="H27" t="s" s="5">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I27" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J27" t="n" s="7">
         <v>8200</v>
@@ -3737,28 +3728,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="10">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F28" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G28" t="n" s="5">
         <v>2023</v>
       </c>
       <c r="H28" t="s" s="5">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I28" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J28" t="n" s="7">
         <v>7100</v>
@@ -3805,7 +3796,7 @@
       <c r="AB28" s="9"/>
       <c r="AC28" s="5"/>
       <c r="AD28" t="s" s="6">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AE28" t="s" s="5">
         <v>45</v>
@@ -3819,28 +3810,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="10">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E29" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F29" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G29" t="n" s="5">
         <v>2023</v>
       </c>
       <c r="H29" t="s" s="5">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I29" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J29" t="n" s="7">
         <v>6800</v>
@@ -3887,7 +3878,7 @@
       <c r="AB29" s="9"/>
       <c r="AC29" s="5"/>
       <c r="AD29" t="s" s="6">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AE29" t="s" s="5">
         <v>45</v>
@@ -3901,28 +3892,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="10">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C30" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D30" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E30" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F30" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G30" t="n" s="5">
         <v>2023</v>
       </c>
       <c r="H30" t="s" s="5">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I30" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J30" t="n" s="7">
         <v>4000</v>
@@ -3969,7 +3960,7 @@
       <c r="AB30" s="9"/>
       <c r="AC30" s="5"/>
       <c r="AD30" t="s" s="6">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AE30" t="s" s="5">
         <v>45</v>
@@ -3983,28 +3974,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="10">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E31" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F31" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G31" t="n" s="5">
         <v>2023</v>
       </c>
       <c r="H31" t="s" s="5">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I31" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J31" t="n" s="7">
         <v>5200</v>
@@ -4065,28 +4056,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="10">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C32" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D32" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F32" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G32" t="n" s="5">
         <v>2022</v>
       </c>
       <c r="H32" t="s" s="5">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I32" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J32" t="n" s="7">
         <v>7000</v>
@@ -4133,7 +4124,7 @@
       <c r="AB32" s="9"/>
       <c r="AC32" s="5"/>
       <c r="AD32" t="s" s="6">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AE32" t="s" s="5">
         <v>45</v>
@@ -4147,28 +4138,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="10">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D33" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E33" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F33" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G33" t="n" s="5">
         <v>2022</v>
       </c>
       <c r="H33" t="s" s="5">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I33" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J33" t="n" s="7">
         <v>8700</v>
@@ -4229,28 +4220,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="s" s="10">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C34" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D34" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E34" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F34" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G34" t="n" s="5">
         <v>2022</v>
       </c>
       <c r="H34" t="s" s="5">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I34" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J34" t="n" s="7">
         <v>8100</v>
@@ -4311,25 +4302,25 @@
         <v>34</v>
       </c>
       <c r="B35" t="s" s="10">
+        <v>150</v>
+      </c>
+      <c r="C35" t="s" s="4">
+        <v>151</v>
+      </c>
+      <c r="D35" t="s" s="4">
         <v>152</v>
-      </c>
-      <c r="C35" t="s" s="4">
-        <v>153</v>
-      </c>
-      <c r="D35" t="s" s="4">
-        <v>154</v>
       </c>
       <c r="E35" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F35" t="s" s="4">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G35" t="n" s="5">
         <v>2020</v>
       </c>
       <c r="H35" t="s" s="5">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" t="n" s="7">
@@ -4377,7 +4368,7 @@
       <c r="AB35" s="9"/>
       <c r="AC35" s="5"/>
       <c r="AD35" t="s" s="6">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AE35" t="s" s="5">
         <v>45</v>
@@ -4391,25 +4382,25 @@
         <v>35</v>
       </c>
       <c r="B36" t="s" s="10">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C36" t="s" s="4">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D36" t="s" s="4">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E36" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F36" t="s" s="4">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G36" t="n" s="5">
         <v>2021</v>
       </c>
       <c r="H36" t="s" s="5">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" t="n" s="7">
@@ -4457,7 +4448,7 @@
       <c r="AB36" s="9"/>
       <c r="AC36" s="5"/>
       <c r="AD36" t="s" s="6">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AE36" t="s" s="5">
         <v>45</v>
@@ -4471,25 +4462,25 @@
         <v>36</v>
       </c>
       <c r="B37" t="s" s="10">
+        <v>159</v>
+      </c>
+      <c r="C37" t="s" s="4">
+        <v>160</v>
+      </c>
+      <c r="D37" t="s" s="4">
         <v>161</v>
       </c>
-      <c r="C37" t="s" s="4">
+      <c r="E37" t="s" s="4">
         <v>162</v>
       </c>
-      <c r="D37" t="s" s="4">
+      <c r="F37" t="s" s="4">
         <v>163</v>
-      </c>
-      <c r="E37" t="s" s="4">
-        <v>164</v>
-      </c>
-      <c r="F37" t="s" s="4">
-        <v>165</v>
       </c>
       <c r="G37" t="n" s="5">
         <v>2020</v>
       </c>
       <c r="H37" t="s" s="5">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I37" s="4"/>
       <c r="J37" t="n" s="7">
@@ -4499,7 +4490,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M37" t="s" s="17">
         <v>53</v>
@@ -4551,25 +4542,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="s" s="10">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C38" t="s" s="4">
+        <v>160</v>
+      </c>
+      <c r="D38" t="s" s="4">
+        <v>161</v>
+      </c>
+      <c r="E38" t="s" s="4">
         <v>162</v>
       </c>
-      <c r="D38" t="s" s="4">
-        <v>163</v>
-      </c>
-      <c r="E38" t="s" s="4">
-        <v>164</v>
-      </c>
       <c r="F38" t="s" s="4">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G38" t="n" s="5">
         <v>2020</v>
       </c>
       <c r="H38" t="s" s="5">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" t="n" s="7">
@@ -4617,7 +4608,7 @@
       <c r="AB38" s="9"/>
       <c r="AC38" s="5"/>
       <c r="AD38" t="s" s="6">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AE38" t="s" s="5">
         <v>45</v>
@@ -4631,25 +4622,25 @@
         <v>38</v>
       </c>
       <c r="B39" t="s" s="10">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C39" t="s" s="4">
+        <v>160</v>
+      </c>
+      <c r="D39" t="s" s="4">
+        <v>161</v>
+      </c>
+      <c r="E39" t="s" s="4">
         <v>162</v>
       </c>
-      <c r="D39" t="s" s="4">
-        <v>163</v>
-      </c>
-      <c r="E39" t="s" s="4">
-        <v>164</v>
-      </c>
       <c r="F39" t="s" s="4">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G39" t="n" s="5">
         <v>2023</v>
       </c>
       <c r="H39" t="s" s="5">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" t="n" s="7">
@@ -4711,25 +4702,25 @@
         <v>39</v>
       </c>
       <c r="B40" t="s" s="10">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C40" t="s" s="4">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D40" t="s" s="4">
+        <v>161</v>
+      </c>
+      <c r="E40" t="s" s="4">
+        <v>174</v>
+      </c>
+      <c r="F40" t="s" s="4">
         <v>163</v>
-      </c>
-      <c r="E40" t="s" s="4">
-        <v>176</v>
-      </c>
-      <c r="F40" t="s" s="4">
-        <v>165</v>
       </c>
       <c r="G40" t="n" s="5">
         <v>2021</v>
       </c>
       <c r="H40" t="s" s="5">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" t="n" s="7">
@@ -4791,28 +4782,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="s" s="10">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C41" t="s" s="4">
+        <v>160</v>
+      </c>
+      <c r="D41" t="s" s="4">
+        <v>161</v>
+      </c>
+      <c r="E41" t="s" s="4">
         <v>162</v>
       </c>
-      <c r="D41" t="s" s="4">
-        <v>163</v>
-      </c>
-      <c r="E41" t="s" s="4">
-        <v>164</v>
-      </c>
       <c r="F41" t="s" s="4">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G41" t="n" s="5">
         <v>2023</v>
       </c>
       <c r="H41" t="s" s="5">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I41" t="s" s="4">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J41" t="n" s="7">
         <v>2800</v>
@@ -4821,7 +4812,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M41" t="s" s="17">
         <v>53</v>
@@ -4873,25 +4864,25 @@
         <v>41</v>
       </c>
       <c r="B42" t="s" s="10">
+        <v>179</v>
+      </c>
+      <c r="C42" t="s" s="4">
+        <v>180</v>
+      </c>
+      <c r="D42" t="s" s="4">
         <v>181</v>
       </c>
-      <c r="C42" t="s" s="4">
+      <c r="E42" t="s" s="4">
         <v>182</v>
       </c>
-      <c r="D42" t="s" s="4">
+      <c r="F42" t="s" s="4">
         <v>183</v>
-      </c>
-      <c r="E42" t="s" s="4">
-        <v>184</v>
-      </c>
-      <c r="F42" t="s" s="4">
-        <v>185</v>
       </c>
       <c r="G42" t="n" s="5">
         <v>2019</v>
       </c>
       <c r="H42" t="s" s="5">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" t="n" s="7">
@@ -4901,7 +4892,7 @@
         <v>0</v>
       </c>
       <c r="L42" t="s" s="4">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M42" t="s" s="17">
         <v>53</v>
@@ -4953,25 +4944,25 @@
         <v>42</v>
       </c>
       <c r="B43" t="s" s="10">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C43" t="s" s="4">
+        <v>180</v>
+      </c>
+      <c r="D43" t="s" s="4">
+        <v>181</v>
+      </c>
+      <c r="E43" t="s" s="4">
         <v>182</v>
       </c>
-      <c r="D43" t="s" s="4">
+      <c r="F43" t="s" s="4">
         <v>183</v>
-      </c>
-      <c r="E43" t="s" s="4">
-        <v>184</v>
-      </c>
-      <c r="F43" t="s" s="4">
-        <v>185</v>
       </c>
       <c r="G43" t="n" s="5">
         <v>2020</v>
       </c>
       <c r="H43" t="s" s="5">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I43" s="4"/>
       <c r="J43" t="n" s="7">
@@ -5033,25 +5024,25 @@
         <v>43</v>
       </c>
       <c r="B44" t="s" s="10">
+        <v>188</v>
+      </c>
+      <c r="C44" t="s" s="4">
+        <v>180</v>
+      </c>
+      <c r="D44" t="s" s="4">
+        <v>181</v>
+      </c>
+      <c r="E44" t="s" s="4">
+        <v>189</v>
+      </c>
+      <c r="F44" t="s" s="4">
         <v>190</v>
-      </c>
-      <c r="C44" t="s" s="4">
-        <v>182</v>
-      </c>
-      <c r="D44" t="s" s="4">
-        <v>183</v>
-      </c>
-      <c r="E44" t="s" s="4">
-        <v>191</v>
-      </c>
-      <c r="F44" t="s" s="4">
-        <v>192</v>
       </c>
       <c r="G44" t="n" s="5">
         <v>2021</v>
       </c>
       <c r="H44" t="s" s="5">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" t="n" s="7">
@@ -5061,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="L44" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M44" t="s" s="17">
         <v>53</v>
@@ -5113,25 +5104,25 @@
         <v>44</v>
       </c>
       <c r="B45" t="s" s="10">
+        <v>192</v>
+      </c>
+      <c r="C45" t="s" s="4">
+        <v>193</v>
+      </c>
+      <c r="D45" t="s" s="4">
         <v>194</v>
       </c>
-      <c r="C45" t="s" s="4">
+      <c r="E45" t="s" s="4">
         <v>195</v>
       </c>
-      <c r="D45" t="s" s="4">
+      <c r="F45" t="s" s="4">
         <v>196</v>
-      </c>
-      <c r="E45" t="s" s="4">
-        <v>197</v>
-      </c>
-      <c r="F45" t="s" s="4">
-        <v>198</v>
       </c>
       <c r="G45" t="n" s="5">
         <v>2019</v>
       </c>
       <c r="H45" t="s" s="5">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I45" s="4"/>
       <c r="J45" t="n" s="7">
@@ -5141,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="s" s="4">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="M45" t="s" s="17">
         <v>53</v>
@@ -5193,25 +5184,25 @@
         <v>45</v>
       </c>
       <c r="B46" t="s" s="10">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C46" t="s" s="4">
+        <v>193</v>
+      </c>
+      <c r="D46" t="s" s="4">
+        <v>194</v>
+      </c>
+      <c r="E46" t="s" s="4">
         <v>195</v>
       </c>
-      <c r="D46" t="s" s="4">
+      <c r="F46" t="s" s="4">
         <v>196</v>
-      </c>
-      <c r="E46" t="s" s="4">
-        <v>197</v>
-      </c>
-      <c r="F46" t="s" s="4">
-        <v>198</v>
       </c>
       <c r="G46" t="n" s="5">
         <v>2020</v>
       </c>
       <c r="H46" t="s" s="5">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" t="n" s="7">
@@ -5221,7 +5212,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="s" s="4">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M46" t="s" s="17">
         <v>53</v>
@@ -5273,25 +5264,25 @@
         <v>46</v>
       </c>
       <c r="B47" t="s" s="10">
+        <v>202</v>
+      </c>
+      <c r="C47" t="s" s="4">
+        <v>193</v>
+      </c>
+      <c r="D47" t="s" s="4">
+        <v>194</v>
+      </c>
+      <c r="E47" t="s" s="4">
+        <v>203</v>
+      </c>
+      <c r="F47" t="s" s="4">
         <v>204</v>
-      </c>
-      <c r="C47" t="s" s="4">
-        <v>195</v>
-      </c>
-      <c r="D47" t="s" s="4">
-        <v>196</v>
-      </c>
-      <c r="E47" t="s" s="4">
-        <v>205</v>
-      </c>
-      <c r="F47" t="s" s="4">
-        <v>206</v>
       </c>
       <c r="G47" t="n" s="5">
         <v>2021</v>
       </c>
       <c r="H47" t="s" s="5">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" t="n" s="7">
@@ -5301,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="L47" t="s" s="4">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M47" t="s" s="17">
         <v>53</v>
@@ -5353,28 +5344,28 @@
         <v>47</v>
       </c>
       <c r="B48" t="s" s="10">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C48" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D48" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E48" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F48" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G48" t="n" s="5">
         <v>2025</v>
       </c>
       <c r="H48" t="s" s="5">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I48" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J48" t="n" s="7">
         <v>0</v>
@@ -5422,7 +5413,7 @@
       <c r="AC48" s="5"/>
       <c r="AD48" s="6"/>
       <c r="AE48" t="s" s="5">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AF48" t="s" s="5">
         <v>46</v>
@@ -5433,16 +5424,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s" s="10">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C49" t="s" s="4">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D49" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E49" t="s" s="4">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="5"/>
@@ -5494,7 +5485,7 @@
       <c r="AC49" s="5"/>
       <c r="AD49" s="6"/>
       <c r="AE49" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF49" t="s" s="5">
         <v>46</v>
@@ -5505,24 +5496,24 @@
         <v>49</v>
       </c>
       <c r="B50" t="s" s="10">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C50" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D50" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E50" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F50" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J50" t="n" s="7">
         <v>0</v>
@@ -5531,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="L50" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M50" t="s" s="17">
         <v>53</v>
@@ -5570,7 +5561,7 @@
       <c r="AC50" s="5"/>
       <c r="AD50" s="6"/>
       <c r="AE50" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF50" t="s" s="5">
         <v>46</v>
@@ -5581,24 +5572,24 @@
         <v>50</v>
       </c>
       <c r="B51" t="s" s="10">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C51" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D51" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E51" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F51" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J51" t="n" s="7">
         <v>0</v>
@@ -5607,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="L51" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M51" t="s" s="17">
         <v>53</v>
@@ -5646,7 +5637,7 @@
       <c r="AC51" s="5"/>
       <c r="AD51" s="6"/>
       <c r="AE51" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF51" t="s" s="5">
         <v>46</v>
@@ -5657,24 +5648,24 @@
         <v>51</v>
       </c>
       <c r="B52" t="s" s="10">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C52" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D52" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E52" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F52" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J52" t="n" s="7">
         <v>0</v>
@@ -5683,7 +5674,7 @@
         <v>0</v>
       </c>
       <c r="L52" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M52" t="s" s="17">
         <v>53</v>
@@ -5722,7 +5713,7 @@
       <c r="AC52" s="5"/>
       <c r="AD52" s="6"/>
       <c r="AE52" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF52" t="s" s="5">
         <v>46</v>
@@ -5733,24 +5724,24 @@
         <v>52</v>
       </c>
       <c r="B53" t="s" s="10">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C53" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D53" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E53" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F53" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J53" t="n" s="7">
         <v>0</v>
@@ -5759,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="L53" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M53" t="s" s="17">
         <v>53</v>
@@ -5798,7 +5789,7 @@
       <c r="AC53" s="5"/>
       <c r="AD53" s="6"/>
       <c r="AE53" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF53" t="s" s="5">
         <v>46</v>
@@ -5809,24 +5800,24 @@
         <v>53</v>
       </c>
       <c r="B54" t="s" s="10">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C54" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D54" t="s" s="4">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E54" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F54" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J54" t="n" s="7">
         <v>0</v>
@@ -5835,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="L54" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M54" t="s" s="17">
         <v>53</v>
@@ -5874,7 +5865,7 @@
       <c r="AC54" s="5"/>
       <c r="AD54" s="6"/>
       <c r="AE54" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF54" t="s" s="5">
         <v>46</v>
@@ -5885,19 +5876,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s" s="10">
+        <v>218</v>
+      </c>
+      <c r="C55" t="s" s="4">
+        <v>219</v>
+      </c>
+      <c r="D55" t="s" s="4">
         <v>220</v>
-      </c>
-      <c r="C55" t="s" s="4">
-        <v>221</v>
-      </c>
-      <c r="D55" t="s" s="4">
-        <v>222</v>
       </c>
       <c r="E55" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F55" t="s" s="4">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G55" t="n" s="5">
         <v>2023</v>
@@ -5915,7 +5906,7 @@
         <v>0</v>
       </c>
       <c r="L55" t="s" s="4">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M55" t="s" s="17">
         <v>53</v>
@@ -5954,7 +5945,7 @@
       <c r="AC55" s="5"/>
       <c r="AD55" s="6"/>
       <c r="AE55" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF55" t="s" s="5">
         <v>46</v>
@@ -5965,23 +5956,23 @@
         <v>55</v>
       </c>
       <c r="B56" t="s" s="10">
+        <v>223</v>
+      </c>
+      <c r="C56" t="s" s="4">
+        <v>224</v>
+      </c>
+      <c r="D56" t="s" s="4">
         <v>225</v>
-      </c>
-      <c r="C56" t="s" s="4">
-        <v>226</v>
-      </c>
-      <c r="D56" t="s" s="4">
-        <v>227</v>
       </c>
       <c r="E56" t="s" s="4">
         <v>48</v>
       </c>
       <c r="F56" t="s" s="4">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" t="s" s="5">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I56" s="4"/>
       <c r="J56" t="n" s="7">
@@ -6030,7 +6021,7 @@
       <c r="AC56" s="5"/>
       <c r="AD56" s="6"/>
       <c r="AE56" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF56" t="s" s="5">
         <v>46</v>
@@ -6041,26 +6032,26 @@
         <v>56</v>
       </c>
       <c r="B57" t="s" s="10">
+        <v>228</v>
+      </c>
+      <c r="C57" t="s" s="4">
+        <v>224</v>
+      </c>
+      <c r="D57" t="s" s="4">
+        <v>225</v>
+      </c>
+      <c r="E57" t="s" s="4">
+        <v>229</v>
+      </c>
+      <c r="F57" t="s" s="4">
         <v>230</v>
-      </c>
-      <c r="C57" t="s" s="4">
-        <v>226</v>
-      </c>
-      <c r="D57" t="s" s="4">
-        <v>227</v>
-      </c>
-      <c r="E57" t="s" s="4">
-        <v>231</v>
-      </c>
-      <c r="F57" t="s" s="4">
-        <v>232</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" t="s" s="5">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I57" t="s" s="4">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J57" t="n" s="7">
         <v>0</v>
@@ -6108,7 +6099,7 @@
       <c r="AC57" s="5"/>
       <c r="AD57" s="6"/>
       <c r="AE57" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF57" t="s" s="5">
         <v>46</v>
@@ -6119,19 +6110,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s" s="10">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C58" t="s" s="4">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D58" t="s" s="4">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E58" t="s" s="4">
         <v>37</v>
       </c>
       <c r="F58" t="s" s="4">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
@@ -6182,7 +6173,7 @@
       <c r="AC58" s="5"/>
       <c r="AD58" s="6"/>
       <c r="AE58" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF58" t="s" s="5">
         <v>46</v>
@@ -6193,19 +6184,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="s" s="10">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C59" t="s" s="4">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D59" t="s" s="4">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E59" t="s" s="4">
         <v>37</v>
       </c>
       <c r="F59" t="s" s="4">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
@@ -6256,7 +6247,7 @@
       <c r="AC59" s="5"/>
       <c r="AD59" s="6"/>
       <c r="AE59" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF59" t="s" s="5">
         <v>46</v>
@@ -6267,13 +6258,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s" s="10">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C60" t="s" s="4">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D60" t="s" s="4">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E60" t="s" s="4">
         <v>48</v>
@@ -6328,7 +6319,7 @@
       <c r="AC60" s="5"/>
       <c r="AD60" s="6"/>
       <c r="AE60" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF60" t="s" s="5">
         <v>46</v>
@@ -6339,19 +6330,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="s" s="10">
+        <v>237</v>
+      </c>
+      <c r="C61" t="s" s="4">
+        <v>238</v>
+      </c>
+      <c r="D61" t="s" s="4">
         <v>239</v>
       </c>
-      <c r="C61" t="s" s="4">
+      <c r="E61" t="s" s="4">
         <v>240</v>
       </c>
-      <c r="D61" t="s" s="4">
-        <v>241</v>
-      </c>
-      <c r="E61" t="s" s="4">
-        <v>242</v>
-      </c>
       <c r="F61" t="s" s="4">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -6402,7 +6393,7 @@
       <c r="AC61" s="5"/>
       <c r="AD61" s="6"/>
       <c r="AE61" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF61" t="s" s="5">
         <v>46</v>
@@ -6413,19 +6404,19 @@
         <v>61</v>
       </c>
       <c r="B62" t="s" s="10">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C62" t="s" s="4">
+        <v>238</v>
+      </c>
+      <c r="D62" t="s" s="4">
+        <v>239</v>
+      </c>
+      <c r="E62" t="s" s="4">
         <v>240</v>
       </c>
-      <c r="D62" t="s" s="4">
-        <v>241</v>
-      </c>
-      <c r="E62" t="s" s="4">
-        <v>242</v>
-      </c>
       <c r="F62" t="s" s="4">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -6476,7 +6467,7 @@
       <c r="AC62" s="5"/>
       <c r="AD62" s="6"/>
       <c r="AE62" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF62" t="s" s="5">
         <v>46</v>
@@ -6487,7 +6478,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s" s="10">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C63" t="s" s="4">
         <v>75</v>
@@ -6496,10 +6487,10 @@
         <v>36</v>
       </c>
       <c r="E63" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="F63" t="s" s="4">
         <v>82</v>
-      </c>
-      <c r="F63" t="s" s="4">
-        <v>83</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -6550,7 +6541,7 @@
       <c r="AC63" s="5"/>
       <c r="AD63" s="6"/>
       <c r="AE63" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF63" t="s" s="5">
         <v>46</v>
@@ -6561,7 +6552,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s" s="10">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C64" t="s" s="4">
         <v>35</v>
@@ -6626,7 +6617,7 @@
       <c r="AC64" s="5"/>
       <c r="AD64" s="6"/>
       <c r="AE64" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF64" t="s" s="5">
         <v>46</v>
@@ -6637,7 +6628,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s" s="10">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C65" t="s" s="4">
         <v>35</v>
@@ -6654,7 +6645,7 @@
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" t="s" s="4">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J65" t="n" s="7">
         <v>0</v>
@@ -6663,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="L65" t="s" s="4">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M65" t="s" s="17">
         <v>53</v>
@@ -6702,7 +6693,7 @@
       <c r="AC65" s="5"/>
       <c r="AD65" s="6"/>
       <c r="AE65" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF65" t="s" s="5">
         <v>46</v>
@@ -6713,19 +6704,17 @@
         <v>65</v>
       </c>
       <c r="B66" t="s" s="10">
+        <v>246</v>
+      </c>
+      <c r="C66" t="s" s="4">
+        <v>247</v>
+      </c>
+      <c r="D66" t="s" s="4">
+        <v>161</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" t="s" s="4">
         <v>248</v>
-      </c>
-      <c r="C66" t="s" s="4">
-        <v>249</v>
-      </c>
-      <c r="D66" t="s" s="4">
-        <v>163</v>
-      </c>
-      <c r="E66" t="s" s="4">
-        <v>250</v>
-      </c>
-      <c r="F66" t="s" s="4">
-        <v>251</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
@@ -6737,7 +6726,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="s" s="4">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="M66" t="s" s="17">
         <v>53</v>
@@ -6776,7 +6765,7 @@
       <c r="AC66" s="5"/>
       <c r="AD66" s="6"/>
       <c r="AE66" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF66" t="s" s="5">
         <v>46</v>
@@ -6787,19 +6776,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s" s="10">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C67" t="s" s="4">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D67" t="s" s="4">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E67" t="s" s="4">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F67" t="s" s="4">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
@@ -6850,7 +6839,7 @@
       <c r="AC67" s="5"/>
       <c r="AD67" s="6"/>
       <c r="AE67" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF67" t="s" s="5">
         <v>46</v>
@@ -6861,19 +6850,19 @@
         <v>67</v>
       </c>
       <c r="B68" t="s" s="10">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C68" t="s" s="4">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D68" t="s" s="4">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E68" t="s" s="4">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F68" t="s" s="4">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -6924,7 +6913,7 @@
       <c r="AC68" s="5"/>
       <c r="AD68" s="6"/>
       <c r="AE68" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF68" t="s" s="5">
         <v>46</v>
@@ -6935,26 +6924,26 @@
         <v>68</v>
       </c>
       <c r="B69" t="s" s="10">
+        <v>255</v>
+      </c>
+      <c r="C69" t="s" s="4">
+        <v>256</v>
+      </c>
+      <c r="D69" t="s" s="4">
+        <v>239</v>
+      </c>
+      <c r="E69" t="s" s="4">
+        <v>257</v>
+      </c>
+      <c r="F69" t="s" s="4">
         <v>258</v>
-      </c>
-      <c r="C69" t="s" s="4">
-        <v>259</v>
-      </c>
-      <c r="D69" t="s" s="4">
-        <v>241</v>
-      </c>
-      <c r="E69" t="s" s="4">
-        <v>260</v>
-      </c>
-      <c r="F69" t="s" s="4">
-        <v>261</v>
       </c>
       <c r="G69" t="n" s="5">
         <v>2021</v>
       </c>
       <c r="H69" s="5"/>
       <c r="I69" t="s" s="4">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="J69" t="n" s="7">
         <v>0</v>
@@ -6963,7 +6952,7 @@
         <v>0</v>
       </c>
       <c r="L69" t="s" s="4">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M69" t="s" s="17">
         <v>53</v>
@@ -7002,7 +6991,7 @@
       <c r="AC69" s="5"/>
       <c r="AD69" s="6"/>
       <c r="AE69" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF69" t="s" s="5">
         <v>46</v>
@@ -7013,24 +7002,24 @@
         <v>69</v>
       </c>
       <c r="B70" t="s" s="10">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C70" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D70" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E70" t="s" s="4">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="F70" t="s" s="4">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
       <c r="I70" t="s" s="4">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J70" t="n" s="7">
         <v>0</v>
@@ -7039,7 +7028,7 @@
         <v>0</v>
       </c>
       <c r="L70" t="s" s="4">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="M70" t="s" s="17">
         <v>53</v>
@@ -7078,7 +7067,7 @@
       <c r="AC70" s="5"/>
       <c r="AD70" s="6"/>
       <c r="AE70" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF70" t="s" s="5">
         <v>46</v>
@@ -7089,19 +7078,19 @@
         <v>70</v>
       </c>
       <c r="B71" t="s" s="10">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C71" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D71" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E71" t="s" s="4">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F71" t="s" s="4">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
@@ -7113,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="L71" t="s" s="4">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="M71" t="s" s="17">
         <v>53</v>
@@ -7152,7 +7141,7 @@
       <c r="AC71" s="5"/>
       <c r="AD71" s="6"/>
       <c r="AE71" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF71" t="s" s="5">
         <v>46</v>
@@ -7163,26 +7152,26 @@
         <v>71</v>
       </c>
       <c r="B72" t="s" s="10">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C72" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D72" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E72" t="s" s="4">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F72" t="s" s="4">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="G72" t="n" s="5">
         <v>2024</v>
       </c>
       <c r="H72" s="5"/>
       <c r="I72" t="s" s="4">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J72" t="n" s="7">
         <v>0</v>
@@ -7191,7 +7180,7 @@
         <v>0</v>
       </c>
       <c r="L72" t="s" s="4">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="M72" t="s" s="17">
         <v>53</v>
@@ -7230,7 +7219,7 @@
       <c r="AC72" s="5"/>
       <c r="AD72" s="6"/>
       <c r="AE72" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF72" t="s" s="5">
         <v>46</v>
@@ -7241,24 +7230,24 @@
         <v>72</v>
       </c>
       <c r="B73" t="s" s="10">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C73" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D73" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E73" t="s" s="4">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F73" t="s" s="4">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" t="s" s="4">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J73" t="n" s="7">
         <v>0</v>
@@ -7306,7 +7295,7 @@
       <c r="AC73" s="5"/>
       <c r="AD73" s="6"/>
       <c r="AE73" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF73" t="s" s="5">
         <v>46</v>
@@ -7317,24 +7306,24 @@
         <v>73</v>
       </c>
       <c r="B74" t="s" s="10">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C74" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D74" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E74" t="s" s="4">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F74" t="s" s="4">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
       <c r="I74" t="s" s="4">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J74" t="n" s="7">
         <v>0</v>
@@ -7343,7 +7332,7 @@
         <v>0</v>
       </c>
       <c r="L74" t="s" s="4">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="M74" t="s" s="17">
         <v>53</v>
@@ -7382,7 +7371,7 @@
       <c r="AC74" s="5"/>
       <c r="AD74" s="6"/>
       <c r="AE74" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF74" t="s" s="5">
         <v>46</v>
@@ -7393,24 +7382,24 @@
         <v>74</v>
       </c>
       <c r="B75" t="s" s="10">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C75" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D75" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E75" t="s" s="4">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F75" t="s" s="4">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" t="s" s="4">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J75" t="n" s="7">
         <v>0</v>
@@ -7419,7 +7408,7 @@
         <v>0</v>
       </c>
       <c r="L75" t="s" s="4">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="M75" t="s" s="17">
         <v>53</v>
@@ -7458,7 +7447,7 @@
       <c r="AC75" s="5"/>
       <c r="AD75" s="6"/>
       <c r="AE75" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF75" t="s" s="5">
         <v>46</v>
@@ -7469,19 +7458,19 @@
         <v>75</v>
       </c>
       <c r="B76" t="s" s="10">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C76" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D76" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E76" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="F76" t="s" s="4">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
@@ -7493,7 +7482,7 @@
         <v>0</v>
       </c>
       <c r="L76" t="s" s="4">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="M76" t="s" s="17">
         <v>53</v>
@@ -7532,7 +7521,7 @@
       <c r="AC76" s="5"/>
       <c r="AD76" s="6"/>
       <c r="AE76" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF76" t="s" s="5">
         <v>46</v>
@@ -7543,19 +7532,19 @@
         <v>76</v>
       </c>
       <c r="B77" t="s" s="10">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C77" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D77" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E77" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="F77" t="s" s="4">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
@@ -7567,7 +7556,7 @@
         <v>0</v>
       </c>
       <c r="L77" t="s" s="4">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="M77" t="s" s="17">
         <v>53</v>
@@ -7606,7 +7595,7 @@
       <c r="AC77" s="5"/>
       <c r="AD77" s="6"/>
       <c r="AE77" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF77" t="s" s="5">
         <v>46</v>
@@ -7617,24 +7606,24 @@
         <v>77</v>
       </c>
       <c r="B78" t="s" s="10">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C78" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D78" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E78" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="F78" t="s" s="4">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
       <c r="I78" t="s" s="4">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J78" t="n" s="7">
         <v>0</v>
@@ -7643,7 +7632,7 @@
         <v>0</v>
       </c>
       <c r="L78" t="s" s="4">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M78" t="s" s="17">
         <v>53</v>
@@ -7682,7 +7671,7 @@
       <c r="AC78" s="5"/>
       <c r="AD78" s="6"/>
       <c r="AE78" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF78" t="s" s="5">
         <v>46</v>
@@ -7693,24 +7682,24 @@
         <v>78</v>
       </c>
       <c r="B79" t="s" s="10">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C79" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D79" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E79" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="F79" t="s" s="4">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
       <c r="I79" t="s" s="4">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J79" t="n" s="7">
         <v>0</v>
@@ -7719,7 +7708,7 @@
         <v>0</v>
       </c>
       <c r="L79" t="s" s="4">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="M79" t="s" s="17">
         <v>53</v>
@@ -7758,7 +7747,7 @@
       <c r="AC79" s="5"/>
       <c r="AD79" s="6"/>
       <c r="AE79" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF79" t="s" s="5">
         <v>46</v>
@@ -7769,19 +7758,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s" s="10">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C80" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D80" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E80" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="F80" t="s" s="4">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -7793,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="L80" t="s" s="4">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M80" t="s" s="17">
         <v>53</v>
@@ -7832,7 +7821,7 @@
       <c r="AC80" s="5"/>
       <c r="AD80" s="6"/>
       <c r="AE80" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF80" t="s" s="5">
         <v>46</v>
@@ -7843,24 +7832,24 @@
         <v>80</v>
       </c>
       <c r="B81" t="s" s="10">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C81" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D81" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E81" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="F81" t="s" s="4">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
       <c r="I81" t="s" s="4">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J81" t="n" s="7">
         <v>0</v>
@@ -7869,7 +7858,7 @@
         <v>0</v>
       </c>
       <c r="L81" t="s" s="4">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="M81" t="s" s="17">
         <v>53</v>
@@ -7908,7 +7897,7 @@
       <c r="AC81" s="5"/>
       <c r="AD81" s="6"/>
       <c r="AE81" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF81" t="s" s="5">
         <v>46</v>
@@ -7919,24 +7908,24 @@
         <v>81</v>
       </c>
       <c r="B82" t="s" s="10">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C82" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D82" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E82" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="F82" t="s" s="4">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
       <c r="I82" t="s" s="4">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="J82" t="n" s="7">
         <v>0</v>
@@ -7945,7 +7934,7 @@
         <v>0</v>
       </c>
       <c r="L82" t="s" s="4">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="M82" t="s" s="17">
         <v>53</v>
@@ -7984,7 +7973,7 @@
       <c r="AC82" s="5"/>
       <c r="AD82" s="6"/>
       <c r="AE82" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF82" t="s" s="5">
         <v>46</v>
@@ -7995,24 +7984,24 @@
         <v>82</v>
       </c>
       <c r="B83" t="s" s="10">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C83" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D83" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E83" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="F83" t="s" s="4">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
       <c r="I83" t="s" s="4">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="J83" t="n" s="7">
         <v>0</v>
@@ -8021,7 +8010,7 @@
         <v>0</v>
       </c>
       <c r="L83" t="s" s="4">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="M83" t="s" s="17">
         <v>53</v>
@@ -8060,7 +8049,7 @@
       <c r="AC83" s="5"/>
       <c r="AD83" s="6"/>
       <c r="AE83" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF83" t="s" s="5">
         <v>46</v>
@@ -8071,24 +8060,24 @@
         <v>83</v>
       </c>
       <c r="B84" t="s" s="10">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C84" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D84" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E84" t="s" s="4">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F84" t="s" s="4">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
       <c r="I84" t="s" s="4">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="J84" t="n" s="7">
         <v>0</v>
@@ -8097,7 +8086,7 @@
         <v>0</v>
       </c>
       <c r="L84" t="s" s="4">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="M84" t="s" s="17">
         <v>53</v>
@@ -8136,7 +8125,7 @@
       <c r="AC84" s="5"/>
       <c r="AD84" s="6"/>
       <c r="AE84" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF84" t="s" s="5">
         <v>46</v>
@@ -8147,24 +8136,24 @@
         <v>84</v>
       </c>
       <c r="B85" t="s" s="10">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C85" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D85" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E85" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="F85" t="s" s="4">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
       <c r="I85" t="s" s="4">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J85" t="n" s="7">
         <v>0</v>
@@ -8173,7 +8162,7 @@
         <v>0</v>
       </c>
       <c r="L85" t="s" s="4">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="M85" t="s" s="17">
         <v>53</v>
@@ -8212,7 +8201,7 @@
       <c r="AC85" s="5"/>
       <c r="AD85" s="6"/>
       <c r="AE85" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF85" t="s" s="5">
         <v>46</v>
@@ -8223,26 +8212,26 @@
         <v>85</v>
       </c>
       <c r="B86" t="s" s="10">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C86" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D86" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E86" t="s" s="4">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F86" t="s" s="4">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G86" t="n" s="5">
         <v>2024</v>
       </c>
       <c r="H86" s="5"/>
       <c r="I86" t="s" s="4">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="J86" t="n" s="7">
         <v>0</v>
@@ -8251,7 +8240,7 @@
         <v>0</v>
       </c>
       <c r="L86" t="s" s="4">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="M86" t="s" s="17">
         <v>53</v>
@@ -8290,7 +8279,7 @@
       <c r="AC86" s="5"/>
       <c r="AD86" s="6"/>
       <c r="AE86" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF86" t="s" s="5">
         <v>46</v>
@@ -8301,24 +8290,24 @@
         <v>86</v>
       </c>
       <c r="B87" t="s" s="10">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C87" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D87" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E87" t="s" s="4">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F87" t="s" s="4">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" t="s" s="4">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="J87" t="n" s="7">
         <v>0</v>
@@ -8327,7 +8316,7 @@
         <v>0</v>
       </c>
       <c r="L87" t="s" s="4">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="M87" t="s" s="17">
         <v>53</v>
@@ -8366,7 +8355,7 @@
       <c r="AC87" s="5"/>
       <c r="AD87" s="6"/>
       <c r="AE87" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF87" t="s" s="5">
         <v>46</v>
@@ -8377,18 +8366,20 @@
         <v>87</v>
       </c>
       <c r="B88" t="s" s="10">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C88" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D88" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E88" t="s" s="4">
-        <v>273</v>
-      </c>
-      <c r="F88" s="4"/>
+        <v>269</v>
+      </c>
+      <c r="F88" t="s" s="4">
+        <v>305</v>
+      </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
       <c r="I88" s="4"/>
@@ -8399,7 +8390,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="s" s="4">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="M88" t="s" s="17">
         <v>53</v>
@@ -8438,7 +8429,7 @@
       <c r="AC88" s="5"/>
       <c r="AD88" s="6"/>
       <c r="AE88" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF88" t="s" s="5">
         <v>46</v>
@@ -8449,24 +8440,24 @@
         <v>88</v>
       </c>
       <c r="B89" t="s" s="10">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C89" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D89" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E89" t="s" s="4">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F89" t="s" s="4">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
       <c r="I89" t="s" s="4">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="J89" t="n" s="7">
         <v>0</v>
@@ -8475,7 +8466,7 @@
         <v>0</v>
       </c>
       <c r="L89" t="s" s="4">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M89" t="s" s="17">
         <v>53</v>
@@ -8514,7 +8505,7 @@
       <c r="AC89" s="5"/>
       <c r="AD89" s="6"/>
       <c r="AE89" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF89" t="s" s="5">
         <v>46</v>
@@ -8525,18 +8516,20 @@
         <v>89</v>
       </c>
       <c r="B90" t="s" s="10">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C90" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D90" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E90" t="s" s="4">
-        <v>273</v>
-      </c>
-      <c r="F90" s="4"/>
+        <v>269</v>
+      </c>
+      <c r="F90" t="s" s="4">
+        <v>305</v>
+      </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5"/>
       <c r="I90" s="4"/>
@@ -8547,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="s" s="4">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="M90" t="s" s="17">
         <v>53</v>
@@ -8586,7 +8579,7 @@
       <c r="AC90" s="5"/>
       <c r="AD90" s="6"/>
       <c r="AE90" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF90" t="s" s="5">
         <v>46</v>
@@ -8597,26 +8590,26 @@
         <v>90</v>
       </c>
       <c r="B91" t="s" s="10">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C91" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D91" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E91" t="s" s="4">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="F91" t="s" s="4">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="G91" t="n" s="5">
         <v>2025</v>
       </c>
       <c r="H91" s="5"/>
       <c r="I91" t="s" s="4">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J91" t="n" s="7">
         <v>0</v>
@@ -8625,7 +8618,7 @@
         <v>0</v>
       </c>
       <c r="L91" t="s" s="4">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M91" t="s" s="17">
         <v>53</v>
@@ -8664,7 +8657,7 @@
       <c r="AC91" s="5"/>
       <c r="AD91" s="6"/>
       <c r="AE91" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF91" t="s" s="5">
         <v>46</v>
@@ -8675,18 +8668,20 @@
         <v>91</v>
       </c>
       <c r="B92" t="s" s="10">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C92" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D92" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E92" t="s" s="4">
-        <v>260</v>
-      </c>
-      <c r="F92" s="4"/>
+        <v>257</v>
+      </c>
+      <c r="F92" t="s" s="4">
+        <v>266</v>
+      </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
       <c r="I92" s="4"/>
@@ -8697,7 +8692,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="s" s="4">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="M92" t="s" s="17">
         <v>53</v>
@@ -8736,7 +8731,7 @@
       <c r="AC92" s="5"/>
       <c r="AD92" s="6"/>
       <c r="AE92" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF92" t="s" s="5">
         <v>46</v>
@@ -8747,18 +8742,20 @@
         <v>92</v>
       </c>
       <c r="B93" t="s" s="10">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C93" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D93" t="s" s="4">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E93" t="s" s="4">
-        <v>260</v>
-      </c>
-      <c r="F93" s="4"/>
+        <v>257</v>
+      </c>
+      <c r="F93" t="s" s="4">
+        <v>266</v>
+      </c>
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
       <c r="I93" s="4"/>
@@ -8769,7 +8766,7 @@
         <v>0</v>
       </c>
       <c r="L93" t="s" s="4">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M93" t="s" s="17">
         <v>53</v>
@@ -8808,7 +8805,7 @@
       <c r="AC93" s="5"/>
       <c r="AD93" s="6"/>
       <c r="AE93" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF93" t="s" s="5">
         <v>46</v>
@@ -8819,26 +8816,26 @@
         <v>93</v>
       </c>
       <c r="B94" t="s" s="10">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C94" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D94" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E94" t="s" s="4">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F94" t="s" s="4">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G94" t="n" s="5">
         <v>2024</v>
       </c>
       <c r="H94" s="5"/>
       <c r="I94" t="s" s="4">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J94" t="n" s="7">
         <v>0</v>
@@ -8886,7 +8883,7 @@
       <c r="AC94" s="5"/>
       <c r="AD94" s="6"/>
       <c r="AE94" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF94" t="s" s="5">
         <v>46</v>
@@ -8897,28 +8894,28 @@
         <v>94</v>
       </c>
       <c r="B95" t="s" s="10">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C95" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D95" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E95" t="s" s="4">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F95" t="s" s="4">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G95" t="n" s="5">
         <v>2024</v>
       </c>
       <c r="H95" t="s" s="5">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="I95" t="s" s="4">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J95" t="n" s="7">
         <v>0</v>
@@ -8966,7 +8963,7 @@
       <c r="AC95" s="5"/>
       <c r="AD95" s="6"/>
       <c r="AE95" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF95" t="s" s="5">
         <v>46</v>
@@ -8977,26 +8974,26 @@
         <v>95</v>
       </c>
       <c r="B96" t="s" s="10">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C96" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D96" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E96" t="s" s="4">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F96" t="s" s="4">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G96" t="n" s="5">
         <v>2024</v>
       </c>
       <c r="H96" s="5"/>
       <c r="I96" t="s" s="4">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J96" t="n" s="7">
         <v>0</v>
@@ -9044,7 +9041,7 @@
       <c r="AC96" s="5"/>
       <c r="AD96" s="6"/>
       <c r="AE96" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF96" t="s" s="5">
         <v>46</v>
@@ -9055,26 +9052,26 @@
         <v>96</v>
       </c>
       <c r="B97" t="s" s="10">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C97" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D97" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E97" t="s" s="4">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F97" t="s" s="4">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G97" t="n" s="5">
         <v>2025</v>
       </c>
       <c r="H97" s="5"/>
       <c r="I97" t="s" s="4">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J97" t="n" s="7">
         <v>0</v>
@@ -9122,7 +9119,7 @@
       <c r="AC97" s="5"/>
       <c r="AD97" s="6"/>
       <c r="AE97" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF97" t="s" s="5">
         <v>46</v>
@@ -9133,28 +9130,28 @@
         <v>97</v>
       </c>
       <c r="B98" t="s" s="10">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C98" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D98" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E98" t="s" s="4">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F98" t="s" s="4">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G98" t="n" s="5">
         <v>2026</v>
       </c>
       <c r="H98" t="s" s="5">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I98" t="s" s="4">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J98" t="n" s="7">
         <v>0</v>
@@ -9202,7 +9199,7 @@
       <c r="AC98" s="5"/>
       <c r="AD98" s="6"/>
       <c r="AE98" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF98" t="s" s="5">
         <v>46</v>
@@ -9213,28 +9210,28 @@
         <v>98</v>
       </c>
       <c r="B99" t="s" s="10">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C99" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D99" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E99" t="s" s="4">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F99" t="s" s="4">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G99" t="n" s="5">
         <v>2027</v>
       </c>
       <c r="H99" t="s" s="5">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="I99" t="s" s="4">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J99" t="n" s="7">
         <v>0</v>
@@ -9282,7 +9279,7 @@
       <c r="AC99" s="5"/>
       <c r="AD99" s="6"/>
       <c r="AE99" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF99" t="s" s="5">
         <v>46</v>
@@ -9293,19 +9290,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="s" s="10">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C100" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D100" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E100" t="s" s="4">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F100" t="s" s="4">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
@@ -9356,7 +9353,7 @@
       <c r="AC100" s="5"/>
       <c r="AD100" s="6"/>
       <c r="AE100" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF100" t="s" s="5">
         <v>46</v>
@@ -9367,19 +9364,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="s" s="10">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C101" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D101" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E101" t="s" s="4">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F101" t="s" s="4">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
@@ -9430,7 +9427,7 @@
       <c r="AC101" s="5"/>
       <c r="AD101" s="6"/>
       <c r="AE101" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF101" t="s" s="5">
         <v>46</v>
@@ -9441,19 +9438,19 @@
         <v>101</v>
       </c>
       <c r="B102" t="s" s="10">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C102" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D102" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E102" t="s" s="4">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F102" t="s" s="4">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="5"/>
@@ -9465,7 +9462,7 @@
         <v>0</v>
       </c>
       <c r="L102" t="s" s="4">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="M102" t="s" s="17">
         <v>53</v>
@@ -9504,7 +9501,7 @@
       <c r="AC102" s="5"/>
       <c r="AD102" s="6"/>
       <c r="AE102" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF102" t="s" s="5">
         <v>46</v>
@@ -9515,19 +9512,19 @@
         <v>102</v>
       </c>
       <c r="B103" t="s" s="10">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C103" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D103" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E103" t="s" s="4">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F103" t="s" s="4">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" t="n" s="5">
@@ -9541,7 +9538,7 @@
         <v>0</v>
       </c>
       <c r="L103" t="s" s="4">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M103" t="s" s="17">
         <v>53</v>
@@ -9580,7 +9577,7 @@
       <c r="AC103" s="5"/>
       <c r="AD103" s="6"/>
       <c r="AE103" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF103" t="s" s="5">
         <v>46</v>
@@ -9591,19 +9588,19 @@
         <v>103</v>
       </c>
       <c r="B104" t="s" s="10">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C104" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D104" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E104" t="s" s="4">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F104" t="s" s="4">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" t="n" s="5">
@@ -9617,7 +9614,7 @@
         <v>0</v>
       </c>
       <c r="L104" t="s" s="4">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M104" t="s" s="17">
         <v>53</v>
@@ -9656,7 +9653,7 @@
       <c r="AC104" s="5"/>
       <c r="AD104" s="6"/>
       <c r="AE104" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF104" t="s" s="5">
         <v>46</v>
@@ -9667,19 +9664,19 @@
         <v>104</v>
       </c>
       <c r="B105" t="s" s="10">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C105" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D105" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E105" t="s" s="4">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F105" t="s" s="4">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" t="n" s="5">
@@ -9693,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="L105" t="s" s="4">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M105" t="s" s="17">
         <v>53</v>
@@ -9732,7 +9729,7 @@
       <c r="AC105" s="5"/>
       <c r="AD105" s="6"/>
       <c r="AE105" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF105" t="s" s="5">
         <v>46</v>
@@ -9743,19 +9740,19 @@
         <v>105</v>
       </c>
       <c r="B106" t="s" s="10">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C106" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D106" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E106" t="s" s="4">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F106" t="s" s="4">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" t="n" s="5">
@@ -9769,7 +9766,7 @@
         <v>0</v>
       </c>
       <c r="L106" t="s" s="4">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M106" t="s" s="17">
         <v>53</v>
@@ -9808,7 +9805,7 @@
       <c r="AC106" s="5"/>
       <c r="AD106" s="6"/>
       <c r="AE106" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF106" t="s" s="5">
         <v>46</v>
@@ -9819,19 +9816,19 @@
         <v>106</v>
       </c>
       <c r="B107" t="s" s="10">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C107" t="s" s="4">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D107" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E107" t="s" s="4">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F107" t="s" s="4">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
@@ -9882,7 +9879,7 @@
       <c r="AC107" s="5"/>
       <c r="AD107" s="6"/>
       <c r="AE107" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF107" t="s" s="5">
         <v>46</v>
@@ -9893,19 +9890,19 @@
         <v>107</v>
       </c>
       <c r="B108" t="s" s="10">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C108" t="s" s="4">
+        <v>346</v>
+      </c>
+      <c r="D108" t="s" s="4">
+        <v>194</v>
+      </c>
+      <c r="E108" t="s" s="4">
         <v>350</v>
       </c>
-      <c r="D108" t="s" s="4">
-        <v>196</v>
-      </c>
-      <c r="E108" t="s" s="4">
-        <v>354</v>
-      </c>
       <c r="F108" t="s" s="4">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
@@ -9917,7 +9914,7 @@
         <v>0</v>
       </c>
       <c r="L108" t="s" s="4">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="M108" t="s" s="17">
         <v>53</v>
@@ -9956,7 +9953,7 @@
       <c r="AC108" s="5"/>
       <c r="AD108" s="6"/>
       <c r="AE108" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF108" t="s" s="5">
         <v>46</v>
@@ -9967,24 +9964,24 @@
         <v>108</v>
       </c>
       <c r="B109" t="s" s="10">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C109" t="s" s="4">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D109" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E109" t="s" s="4">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F109" t="s" s="4">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
       <c r="I109" t="s" s="4">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="J109" t="n" s="7">
         <v>0</v>
@@ -10032,7 +10029,7 @@
       <c r="AC109" s="5"/>
       <c r="AD109" s="6"/>
       <c r="AE109" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF109" t="s" s="5">
         <v>46</v>
@@ -10043,18 +10040,18 @@
         <v>109</v>
       </c>
       <c r="B110" t="s" s="10">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C110" t="s" s="4">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D110" t="s" s="4">
-        <v>196</v>
-      </c>
-      <c r="E110" t="s" s="4">
-        <v>359</v>
-      </c>
-      <c r="F110" s="4"/>
+        <v>194</v>
+      </c>
+      <c r="E110" s="4"/>
+      <c r="F110" t="s" s="4">
+        <v>355</v>
+      </c>
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
       <c r="I110" s="4"/>
@@ -10104,7 +10101,7 @@
       <c r="AC110" s="5"/>
       <c r="AD110" s="6"/>
       <c r="AE110" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF110" t="s" s="5">
         <v>46</v>
@@ -10115,24 +10112,24 @@
         <v>110</v>
       </c>
       <c r="B111" t="s" s="10">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C111" t="s" s="4">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D111" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E111" t="s" s="4">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F111" t="s" s="4">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="5"/>
       <c r="I111" t="s" s="4">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="J111" t="n" s="7">
         <v>0</v>
@@ -10180,7 +10177,7 @@
       <c r="AC111" s="5"/>
       <c r="AD111" s="6"/>
       <c r="AE111" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF111" t="s" s="5">
         <v>46</v>
@@ -10191,13 +10188,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s" s="10">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C112" t="s" s="4">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D112" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
@@ -10211,7 +10208,7 @@
         <v>0</v>
       </c>
       <c r="L112" t="s" s="4">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="M112" t="s" s="17">
         <v>53</v>
@@ -10250,7 +10247,7 @@
       <c r="AC112" s="5"/>
       <c r="AD112" s="6"/>
       <c r="AE112" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF112" t="s" s="5">
         <v>46</v>
@@ -10261,28 +10258,28 @@
         <v>112</v>
       </c>
       <c r="B113" t="s" s="10">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C113" t="s" s="4">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D113" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E113" t="s" s="4">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F113" t="s" s="4">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="G113" t="n" s="5">
         <v>2024</v>
       </c>
       <c r="H113" t="s" s="5">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I113" t="s" s="4">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="J113" t="n" s="7">
         <v>0</v>
@@ -10330,7 +10327,7 @@
       <c r="AC113" s="5"/>
       <c r="AD113" s="6"/>
       <c r="AE113" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF113" t="s" s="5">
         <v>46</v>
@@ -10341,18 +10338,20 @@
         <v>113</v>
       </c>
       <c r="B114" t="s" s="10">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C114" t="s" s="4">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D114" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E114" t="s" s="4">
-        <v>373</v>
-      </c>
-      <c r="F114" s="4"/>
+        <v>369</v>
+      </c>
+      <c r="F114" t="s" s="4">
+        <v>370</v>
+      </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
       <c r="I114" s="4"/>
@@ -10363,7 +10362,7 @@
         <v>0</v>
       </c>
       <c r="L114" t="s" s="4">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="M114" t="s" s="17">
         <v>53</v>
@@ -10402,7 +10401,7 @@
       <c r="AC114" s="5"/>
       <c r="AD114" s="6"/>
       <c r="AE114" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF114" t="s" s="5">
         <v>46</v>
@@ -10413,23 +10412,23 @@
         <v>114</v>
       </c>
       <c r="B115" t="s" s="10">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C115" t="s" s="4">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D115" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E115" t="s" s="4">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="F115" t="s" s="4">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="G115" s="5"/>
       <c r="H115" t="s" s="5">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="I115" s="4"/>
       <c r="J115" t="n" s="7">
@@ -10439,7 +10438,7 @@
         <v>0</v>
       </c>
       <c r="L115" t="s" s="4">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="M115" t="s" s="17">
         <v>53</v>
@@ -10478,7 +10477,7 @@
       <c r="AC115" s="5"/>
       <c r="AD115" s="6"/>
       <c r="AE115" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF115" t="s" s="5">
         <v>46</v>
@@ -10489,20 +10488,20 @@
         <v>115</v>
       </c>
       <c r="B116" t="s" s="10">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C116" t="s" s="4">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D116" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
       <c r="I116" t="s" s="4">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="J116" t="n" s="7">
         <v>0</v>
@@ -10511,7 +10510,7 @@
         <v>0</v>
       </c>
       <c r="L116" t="s" s="4">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="M116" t="s" s="17">
         <v>53</v>
@@ -10550,7 +10549,7 @@
       <c r="AC116" s="5"/>
       <c r="AD116" s="6"/>
       <c r="AE116" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF116" t="s" s="5">
         <v>46</v>
@@ -10561,17 +10560,17 @@
         <v>116</v>
       </c>
       <c r="B117" t="s" s="10">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C117" t="s" s="4">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D117" t="s" s="4">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E117" s="4"/>
       <c r="F117" t="s" s="4">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="G117" t="n" s="5">
         <v>2024</v>
@@ -10622,7 +10621,7 @@
       <c r="AC117" s="5"/>
       <c r="AD117" s="6"/>
       <c r="AE117" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF117" t="s" s="5">
         <v>46</v>
@@ -10633,21 +10632,21 @@
         <v>117</v>
       </c>
       <c r="B118" t="s" s="10">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C118" t="s" s="4">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D118" t="s" s="4">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E118" s="4"/>
       <c r="F118" t="s" s="4">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" t="s" s="5">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I118" s="4"/>
       <c r="J118" t="n" s="7">
@@ -10694,7 +10693,7 @@
       <c r="AC118" s="5"/>
       <c r="AD118" s="6"/>
       <c r="AE118" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF118" t="s" s="5">
         <v>46</v>
@@ -10705,18 +10704,20 @@
         <v>118</v>
       </c>
       <c r="B119" t="s" s="10">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C119" t="s" s="4">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D119" t="s" s="4">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E119" t="s" s="4">
-        <v>390</v>
-      </c>
-      <c r="F119" s="4"/>
+        <v>386</v>
+      </c>
+      <c r="F119" t="s" s="4">
+        <v>387</v>
+      </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
       <c r="I119" s="4"/>
@@ -10766,7 +10767,7 @@
       <c r="AC119" s="5"/>
       <c r="AD119" s="6"/>
       <c r="AE119" t="s" s="5">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AF119" t="s" s="5">
         <v>46</v>
@@ -10774,10 +10775,10 @@
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" t="s" s="21">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B120" t="s" s="22">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C120" s="21"/>
       <c r="D120" s="21"/>
@@ -10858,46 +10859,46 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" t="s" s="3">
+        <v>390</v>
+      </c>
+      <c r="B1" t="s" s="3">
+        <v>391</v>
+      </c>
+      <c r="C1" t="s" s="3">
+        <v>392</v>
+      </c>
+      <c r="D1" t="s" s="3">
         <v>393</v>
       </c>
-      <c r="B1" t="s" s="3">
+      <c r="E1" t="s" s="3">
         <v>394</v>
       </c>
-      <c r="C1" t="s" s="3">
+      <c r="F1" t="s" s="3">
         <v>395</v>
       </c>
-      <c r="D1" t="s" s="3">
+      <c r="G1" t="s" s="3">
         <v>396</v>
       </c>
-      <c r="E1" t="s" s="3">
+      <c r="H1" t="s" s="3">
         <v>397</v>
       </c>
-      <c r="F1" t="s" s="3">
+      <c r="I1" t="s" s="3">
         <v>398</v>
       </c>
-      <c r="G1" t="s" s="3">
+      <c r="J1" t="s" s="3">
         <v>399</v>
       </c>
-      <c r="H1" t="s" s="3">
+      <c r="K1" t="s" s="3">
         <v>400</v>
       </c>
-      <c r="I1" t="s" s="3">
+      <c r="L1" t="s" s="3">
         <v>401</v>
       </c>
-      <c r="J1" t="s" s="3">
+      <c r="M1" t="s" s="3">
         <v>402</v>
       </c>
-      <c r="K1" t="s" s="3">
+      <c r="N1" t="s" s="3">
         <v>403</v>
-      </c>
-      <c r="L1" t="s" s="3">
-        <v>404</v>
-      </c>
-      <c r="M1" t="s" s="3">
-        <v>405</v>
-      </c>
-      <c r="N1" t="s" s="3">
-        <v>406</v>
       </c>
     </row>
     <row r="2">
@@ -11146,19 +11147,19 @@
         <v>75</v>
       </c>
       <c r="C8" t="s" s="4">
+        <v>56</v>
+      </c>
+      <c r="D8" t="s" s="4">
         <v>76</v>
-      </c>
-      <c r="D8" t="s" s="4">
-        <v>77</v>
       </c>
       <c r="E8" t="n" s="5">
         <v>2018</v>
       </c>
       <c r="F8" t="s" s="5">
+        <v>77</v>
+      </c>
+      <c r="G8" t="s" s="4">
         <v>78</v>
-      </c>
-      <c r="G8" t="s" s="4">
-        <v>79</v>
       </c>
       <c r="H8" t="n" s="7">
         <v>21900</v>
@@ -11175,30 +11176,30 @@
       <c r="L8" s="9"/>
       <c r="M8" s="9"/>
       <c r="N8" t="s" s="6">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="10">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s" s="4">
         <v>75</v>
       </c>
       <c r="C9" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="D9" t="s" s="4">
         <v>82</v>
-      </c>
-      <c r="D9" t="s" s="4">
-        <v>83</v>
       </c>
       <c r="E9" t="n" s="5">
         <v>2019</v>
       </c>
       <c r="F9" t="s" s="5">
+        <v>83</v>
+      </c>
+      <c r="G9" t="s" s="4">
         <v>84</v>
-      </c>
-      <c r="G9" t="s" s="4">
-        <v>85</v>
       </c>
       <c r="H9" t="n" s="7">
         <v>19200</v>
@@ -11215,30 +11216,30 @@
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
       <c r="N9" t="s" s="6">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="10">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s" s="4">
         <v>75</v>
       </c>
       <c r="C10" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="D10" t="s" s="4">
         <v>82</v>
-      </c>
-      <c r="D10" t="s" s="4">
-        <v>83</v>
       </c>
       <c r="E10" t="n" s="5">
         <v>2020</v>
       </c>
       <c r="F10" t="s" s="5">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s" s="4">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H10" t="n" s="7">
         <v>16700</v>
@@ -11255,30 +11256,30 @@
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
       <c r="N10" t="s" s="6">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="10">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s" s="4">
         <v>75</v>
       </c>
       <c r="C11" t="s" s="4">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s" s="4">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E11" t="n" s="5">
         <v>2020</v>
       </c>
       <c r="F11" t="s" s="5">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G11" t="s" s="4">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H11" t="n" s="7">
         <v>13200</v>
@@ -11295,30 +11296,30 @@
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" t="s" s="6">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="10">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B12" t="s" s="4">
         <v>75</v>
       </c>
       <c r="C12" t="s" s="4">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s" s="4">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E12" t="n" s="5">
         <v>2021</v>
       </c>
       <c r="F12" t="s" s="5">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G12" t="s" s="4">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H12" t="n" s="7">
         <v>11800</v>
@@ -11335,27 +11336,27 @@
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
       <c r="N12" t="s" s="6">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="10">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B13" t="s" s="4">
         <v>75</v>
       </c>
       <c r="C13" t="s" s="4">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s" s="4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E13" t="n" s="5">
         <v>2021</v>
       </c>
       <c r="F13" t="s" s="5">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" t="n" s="7">
@@ -11378,22 +11379,22 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="10">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B14" t="s" s="4">
         <v>75</v>
       </c>
       <c r="C14" t="s" s="4">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s" s="4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E14" t="n" s="5">
         <v>2022</v>
       </c>
       <c r="F14" t="s" s="5">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" t="n" s="7">
@@ -11416,10 +11417,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="10">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B15" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s" s="4">
         <v>56</v>
@@ -11431,7 +11432,7 @@
         <v>2019</v>
       </c>
       <c r="F15" t="s" s="5">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G15" t="s" s="4">
         <v>59</v>
@@ -11454,10 +11455,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="10">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s" s="4">
         <v>56</v>
@@ -11469,7 +11470,7 @@
         <v>2019</v>
       </c>
       <c r="F16" t="s" s="5">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G16" t="s" s="4">
         <v>59</v>
@@ -11494,10 +11495,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="10">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B17" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s" s="4">
         <v>56</v>
@@ -11509,7 +11510,7 @@
         <v>2020</v>
       </c>
       <c r="F17" t="s" s="5">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G17" t="s" s="4">
         <v>59</v>
@@ -11534,10 +11535,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="10">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s" s="4">
         <v>56</v>
@@ -11549,7 +11550,7 @@
         <v>2020</v>
       </c>
       <c r="F18" t="s" s="5">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G18" t="s" s="4">
         <v>59</v>
@@ -11569,15 +11570,15 @@
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
       <c r="N18" t="s" s="6">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="10">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B19" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s" s="4">
         <v>56</v>
@@ -11589,7 +11590,7 @@
         <v>2020</v>
       </c>
       <c r="F19" t="s" s="5">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G19" t="s" s="4">
         <v>59</v>
@@ -11601,7 +11602,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="s" s="4">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K19" t="s" s="17">
         <v>53</v>
@@ -11614,10 +11615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="10">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s" s="4">
         <v>56</v>
@@ -11629,7 +11630,7 @@
         <v>2021</v>
       </c>
       <c r="F20" t="s" s="5">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G20" t="s" s="4">
         <v>59</v>
@@ -11641,7 +11642,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="s" s="4">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K20" t="s" s="18">
         <v>42</v>
@@ -11649,15 +11650,15 @@
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
       <c r="N20" t="s" s="6">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="10">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B21" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s" s="4">
         <v>56</v>
@@ -11669,7 +11670,7 @@
         <v>2021</v>
       </c>
       <c r="F21" t="s" s="5">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G21" t="s" s="4">
         <v>59</v>
@@ -11689,15 +11690,15 @@
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
       <c r="N21" t="s" s="6">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="10">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s" s="4">
         <v>56</v>
@@ -11709,7 +11710,7 @@
         <v>2021</v>
       </c>
       <c r="F22" t="s" s="5">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G22" t="s" s="4">
         <v>59</v>
@@ -11734,25 +11735,25 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="10">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B23" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D23" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E23" t="n" s="5">
         <v>2022</v>
       </c>
       <c r="F23" t="s" s="5">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G23" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H23" t="n" s="7">
         <v>9800</v>
@@ -11774,25 +11775,25 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="10">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B24" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D24" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E24" t="n" s="5">
         <v>2022</v>
       </c>
       <c r="F24" t="s" s="5">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G24" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H24" t="n" s="7">
         <v>8900</v>
@@ -11814,25 +11815,25 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="10">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B25" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D25" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E25" t="n" s="5">
         <v>2022</v>
       </c>
       <c r="F25" t="s" s="5">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G25" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H25" t="n" s="7">
         <v>8200</v>
@@ -11854,25 +11855,25 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="10">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D26" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E26" t="n" s="5">
         <v>2023</v>
       </c>
       <c r="F26" t="s" s="5">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G26" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H26" t="n" s="7">
         <v>7100</v>
@@ -11889,30 +11890,30 @@
       <c r="L26" s="9"/>
       <c r="M26" s="9"/>
       <c r="N26" t="s" s="6">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="10">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B27" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D27" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E27" t="n" s="5">
         <v>2023</v>
       </c>
       <c r="F27" t="s" s="5">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G27" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H27" t="n" s="7">
         <v>6800</v>
@@ -11929,30 +11930,30 @@
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
       <c r="N27" t="s" s="6">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="10">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B28" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D28" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E28" t="n" s="5">
         <v>2023</v>
       </c>
       <c r="F28" t="s" s="5">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G28" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H28" t="n" s="7">
         <v>4000</v>
@@ -11969,30 +11970,30 @@
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
       <c r="N28" t="s" s="6">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="10">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B29" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D29" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E29" t="n" s="5">
         <v>2023</v>
       </c>
       <c r="F29" t="s" s="5">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G29" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H29" t="n" s="7">
         <v>5200</v>
@@ -12014,25 +12015,25 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="10">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B30" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D30" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E30" t="n" s="5">
         <v>2022</v>
       </c>
       <c r="F30" t="s" s="5">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G30" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H30" t="n" s="7">
         <v>7000</v>
@@ -12049,30 +12050,30 @@
       <c r="L30" s="9"/>
       <c r="M30" s="9"/>
       <c r="N30" t="s" s="6">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="10">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B31" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D31" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E31" t="n" s="5">
         <v>2022</v>
       </c>
       <c r="F31" t="s" s="5">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G31" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H31" t="n" s="7">
         <v>8700</v>
@@ -12094,25 +12095,25 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="10">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B32" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D32" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E32" t="n" s="5">
         <v>2022</v>
       </c>
       <c r="F32" t="s" s="5">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G32" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H32" t="n" s="7">
         <v>8100</v>
@@ -12134,22 +12135,22 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="10">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B33" t="s" s="4">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C33" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D33" t="s" s="4">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E33" t="n" s="5">
         <v>2020</v>
       </c>
       <c r="F33" t="s" s="5">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" t="n" s="7">
@@ -12167,27 +12168,27 @@
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
       <c r="N33" t="s" s="6">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="10">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B34" t="s" s="4">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C34" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D34" t="s" s="4">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E34" t="n" s="5">
         <v>2021</v>
       </c>
       <c r="F34" t="s" s="5">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" t="n" s="7">
@@ -12205,27 +12206,27 @@
       <c r="L34" s="9"/>
       <c r="M34" s="9"/>
       <c r="N34" t="s" s="6">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="10">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B35" t="s" s="4">
+        <v>160</v>
+      </c>
+      <c r="C35" t="s" s="4">
         <v>162</v>
       </c>
-      <c r="C35" t="s" s="4">
-        <v>164</v>
-      </c>
       <c r="D35" t="s" s="4">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E35" t="n" s="5">
         <v>2020</v>
       </c>
       <c r="F35" t="s" s="5">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" t="n" s="7">
@@ -12235,7 +12236,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K35" t="s" s="17">
         <v>53</v>
@@ -12248,22 +12249,22 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="10">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B36" t="s" s="4">
+        <v>160</v>
+      </c>
+      <c r="C36" t="s" s="4">
         <v>162</v>
       </c>
-      <c r="C36" t="s" s="4">
-        <v>164</v>
-      </c>
       <c r="D36" t="s" s="4">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E36" t="n" s="5">
         <v>2020</v>
       </c>
       <c r="F36" t="s" s="5">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G36" s="4"/>
       <c r="H36" t="n" s="7">
@@ -12281,27 +12282,27 @@
       <c r="L36" s="9"/>
       <c r="M36" s="9"/>
       <c r="N36" t="s" s="6">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="10">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B37" t="s" s="4">
+        <v>160</v>
+      </c>
+      <c r="C37" t="s" s="4">
         <v>162</v>
       </c>
-      <c r="C37" t="s" s="4">
-        <v>164</v>
-      </c>
       <c r="D37" t="s" s="4">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E37" t="n" s="5">
         <v>2023</v>
       </c>
       <c r="F37" t="s" s="5">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" t="n" s="7">
@@ -12324,22 +12325,22 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="10">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B38" t="s" s="4">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C38" t="s" s="4">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D38" t="s" s="4">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E38" t="n" s="5">
         <v>2021</v>
       </c>
       <c r="F38" t="s" s="5">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" t="n" s="7">
@@ -12362,25 +12363,25 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="10">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B39" t="s" s="4">
+        <v>160</v>
+      </c>
+      <c r="C39" t="s" s="4">
         <v>162</v>
       </c>
-      <c r="C39" t="s" s="4">
-        <v>164</v>
-      </c>
       <c r="D39" t="s" s="4">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E39" t="n" s="5">
         <v>2023</v>
       </c>
       <c r="F39" t="s" s="5">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G39" t="s" s="4">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H39" t="n" s="7">
         <v>2800</v>
@@ -12389,7 +12390,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K39" t="s" s="17">
         <v>53</v>
@@ -12402,22 +12403,22 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="10">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B40" t="s" s="4">
+        <v>180</v>
+      </c>
+      <c r="C40" t="s" s="4">
         <v>182</v>
       </c>
-      <c r="C40" t="s" s="4">
-        <v>184</v>
-      </c>
       <c r="D40" t="s" s="4">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E40" t="n" s="5">
         <v>2019</v>
       </c>
       <c r="F40" t="s" s="5">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" t="n" s="7">
@@ -12427,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="s" s="4">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K40" t="s" s="17">
         <v>53</v>
@@ -12440,22 +12441,22 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="10">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B41" t="s" s="4">
+        <v>180</v>
+      </c>
+      <c r="C41" t="s" s="4">
         <v>182</v>
       </c>
-      <c r="C41" t="s" s="4">
-        <v>184</v>
-      </c>
       <c r="D41" t="s" s="4">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E41" t="n" s="5">
         <v>2020</v>
       </c>
       <c r="F41" t="s" s="5">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G41" s="4"/>
       <c r="H41" t="n" s="7">
@@ -12478,22 +12479,22 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="10">
+        <v>188</v>
+      </c>
+      <c r="B42" t="s" s="4">
+        <v>180</v>
+      </c>
+      <c r="C42" t="s" s="4">
+        <v>189</v>
+      </c>
+      <c r="D42" t="s" s="4">
         <v>190</v>
-      </c>
-      <c r="B42" t="s" s="4">
-        <v>182</v>
-      </c>
-      <c r="C42" t="s" s="4">
-        <v>191</v>
-      </c>
-      <c r="D42" t="s" s="4">
-        <v>192</v>
       </c>
       <c r="E42" t="n" s="5">
         <v>2021</v>
       </c>
       <c r="F42" t="s" s="5">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" t="n" s="7">
@@ -12503,7 +12504,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K42" t="s" s="17">
         <v>53</v>
@@ -12516,22 +12517,22 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="10">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B43" t="s" s="4">
+        <v>193</v>
+      </c>
+      <c r="C43" t="s" s="4">
         <v>195</v>
       </c>
-      <c r="C43" t="s" s="4">
-        <v>197</v>
-      </c>
       <c r="D43" t="s" s="4">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E43" t="n" s="5">
         <v>2019</v>
       </c>
       <c r="F43" t="s" s="5">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" t="n" s="7">
@@ -12541,7 +12542,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="s" s="4">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="K43" t="s" s="17">
         <v>53</v>
@@ -12554,22 +12555,22 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="10">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B44" t="s" s="4">
+        <v>193</v>
+      </c>
+      <c r="C44" t="s" s="4">
         <v>195</v>
       </c>
-      <c r="C44" t="s" s="4">
-        <v>197</v>
-      </c>
       <c r="D44" t="s" s="4">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E44" t="n" s="5">
         <v>2020</v>
       </c>
       <c r="F44" t="s" s="5">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" t="n" s="7">
@@ -12579,7 +12580,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="s" s="4">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K44" t="s" s="17">
         <v>53</v>
@@ -12592,22 +12593,22 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="10">
+        <v>202</v>
+      </c>
+      <c r="B45" t="s" s="4">
+        <v>193</v>
+      </c>
+      <c r="C45" t="s" s="4">
+        <v>203</v>
+      </c>
+      <c r="D45" t="s" s="4">
         <v>204</v>
-      </c>
-      <c r="B45" t="s" s="4">
-        <v>195</v>
-      </c>
-      <c r="C45" t="s" s="4">
-        <v>205</v>
-      </c>
-      <c r="D45" t="s" s="4">
-        <v>206</v>
       </c>
       <c r="E45" t="n" s="5">
         <v>2021</v>
       </c>
       <c r="F45" t="s" s="5">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" t="n" s="7">
@@ -12617,7 +12618,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="s" s="4">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K45" t="s" s="17">
         <v>53</v>
@@ -12630,25 +12631,25 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="10">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B46" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C46" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D46" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E46" t="n" s="5">
         <v>2025</v>
       </c>
       <c r="F46" t="s" s="5">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G46" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H46" t="n" s="7">
         <v>0</v>
@@ -12668,13 +12669,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="10">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B47" t="s" s="4">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C47" t="s" s="4">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="5"/>
@@ -12698,21 +12699,21 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="10">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B48" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C48" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D48" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H48" t="n" s="7">
         <v>0</v>
@@ -12721,7 +12722,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K48" t="s" s="17">
         <v>53</v>
@@ -12732,21 +12733,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="10">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B49" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C49" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D49" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H49" t="n" s="7">
         <v>0</v>
@@ -12755,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K49" t="s" s="17">
         <v>53</v>
@@ -12766,21 +12767,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="10">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B50" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C50" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D50" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
       <c r="G50" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H50" t="n" s="7">
         <v>0</v>
@@ -12789,7 +12790,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K50" t="s" s="17">
         <v>53</v>
@@ -12800,21 +12801,21 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="10">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B51" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C51" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D51" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H51" t="n" s="7">
         <v>0</v>
@@ -12823,7 +12824,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K51" t="s" s="17">
         <v>53</v>
@@ -12834,21 +12835,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="10">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B52" t="s" s="4">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C52" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D52" t="s" s="4">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" t="s" s="4">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H52" t="n" s="7">
         <v>0</v>
@@ -12857,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="s" s="4">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K52" t="s" s="17">
         <v>53</v>
@@ -12868,16 +12869,16 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="10">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B53" t="s" s="4">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C53" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D53" t="s" s="4">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E53" t="n" s="5">
         <v>2023</v>
@@ -12895,7 +12896,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="s" s="4">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K53" t="s" s="17">
         <v>53</v>
@@ -12906,20 +12907,20 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="10">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B54" t="s" s="4">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C54" t="s" s="4">
         <v>48</v>
       </c>
       <c r="D54" t="s" s="4">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" t="s" s="5">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" t="n" s="7">
@@ -12940,23 +12941,23 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="10">
+        <v>228</v>
+      </c>
+      <c r="B55" t="s" s="4">
+        <v>224</v>
+      </c>
+      <c r="C55" t="s" s="4">
+        <v>229</v>
+      </c>
+      <c r="D55" t="s" s="4">
         <v>230</v>
-      </c>
-      <c r="B55" t="s" s="4">
-        <v>226</v>
-      </c>
-      <c r="C55" t="s" s="4">
-        <v>231</v>
-      </c>
-      <c r="D55" t="s" s="4">
-        <v>232</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" t="s" s="5">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G55" t="s" s="4">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H55" t="n" s="7">
         <v>0</v>
@@ -12976,16 +12977,16 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="10">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B56" t="s" s="4">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C56" t="s" s="4">
         <v>37</v>
       </c>
       <c r="D56" t="s" s="4">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
@@ -13008,16 +13009,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="10">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B57" t="s" s="4">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C57" t="s" s="4">
         <v>37</v>
       </c>
       <c r="D57" t="s" s="4">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
@@ -13040,10 +13041,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="10">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B58" t="s" s="4">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C58" t="s" s="4">
         <v>48</v>
@@ -13070,16 +13071,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="10">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B59" t="s" s="4">
+        <v>238</v>
+      </c>
+      <c r="C59" t="s" s="4">
         <v>240</v>
       </c>
-      <c r="C59" t="s" s="4">
-        <v>242</v>
-      </c>
       <c r="D59" t="s" s="4">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
@@ -13102,16 +13103,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="10">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B60" t="s" s="4">
+        <v>238</v>
+      </c>
+      <c r="C60" t="s" s="4">
         <v>240</v>
       </c>
-      <c r="C60" t="s" s="4">
-        <v>242</v>
-      </c>
       <c r="D60" t="s" s="4">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
@@ -13134,16 +13135,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="10">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B61" t="s" s="4">
         <v>75</v>
       </c>
       <c r="C61" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="D61" t="s" s="4">
         <v>82</v>
-      </c>
-      <c r="D61" t="s" s="4">
-        <v>83</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
@@ -13166,7 +13167,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="10">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B62" t="s" s="4">
         <v>35</v>
@@ -13200,7 +13201,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="10">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B63" t="s" s="4">
         <v>35</v>
@@ -13214,7 +13215,7 @@
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
       <c r="G63" t="s" s="4">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H63" t="n" s="7">
         <v>0</v>
@@ -13223,7 +13224,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="s" s="4">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K63" t="s" s="17">
         <v>53</v>
@@ -13234,16 +13235,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="10">
+        <v>246</v>
+      </c>
+      <c r="B64" t="s" s="4">
+        <v>247</v>
+      </c>
+      <c r="C64" s="4"/>
+      <c r="D64" t="s" s="4">
         <v>248</v>
-      </c>
-      <c r="B64" t="s" s="4">
-        <v>249</v>
-      </c>
-      <c r="C64" t="s" s="4">
-        <v>250</v>
-      </c>
-      <c r="D64" t="s" s="4">
-        <v>251</v>
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
@@ -13255,7 +13254,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="s" s="4">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="K64" t="s" s="17">
         <v>53</v>
@@ -13266,16 +13265,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="10">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B65" t="s" s="4">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C65" t="s" s="4">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D65" t="s" s="4">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
@@ -13298,16 +13297,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="10">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B66" t="s" s="4">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C66" t="s" s="4">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D66" t="s" s="4">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
@@ -13330,23 +13329,23 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="10">
+        <v>255</v>
+      </c>
+      <c r="B67" t="s" s="4">
+        <v>256</v>
+      </c>
+      <c r="C67" t="s" s="4">
+        <v>257</v>
+      </c>
+      <c r="D67" t="s" s="4">
         <v>258</v>
-      </c>
-      <c r="B67" t="s" s="4">
-        <v>259</v>
-      </c>
-      <c r="C67" t="s" s="4">
-        <v>260</v>
-      </c>
-      <c r="D67" t="s" s="4">
-        <v>261</v>
       </c>
       <c r="E67" t="n" s="5">
         <v>2021</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" t="s" s="4">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H67" t="n" s="7">
         <v>0</v>
@@ -13355,7 +13354,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="s" s="4">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="K67" t="s" s="17">
         <v>53</v>
@@ -13366,21 +13365,21 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="10">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B68" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C68" t="s" s="4">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="D68" t="s" s="4">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
       <c r="G68" t="s" s="4">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H68" t="n" s="7">
         <v>0</v>
@@ -13389,7 +13388,7 @@
         <v>0</v>
       </c>
       <c r="J68" t="s" s="4">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="K68" t="s" s="17">
         <v>53</v>
@@ -13400,16 +13399,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="10">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B69" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C69" t="s" s="4">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D69" t="s" s="4">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
@@ -13421,7 +13420,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="s" s="4">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K69" t="s" s="17">
         <v>53</v>
@@ -13432,23 +13431,23 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="10">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B70" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C70" t="s" s="4">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D70" t="s" s="4">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E70" t="n" s="5">
         <v>2024</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" t="s" s="4">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H70" t="n" s="7">
         <v>0</v>
@@ -13457,7 +13456,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="s" s="4">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="K70" t="s" s="17">
         <v>53</v>
@@ -13468,21 +13467,21 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="10">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B71" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C71" t="s" s="4">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D71" t="s" s="4">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
       <c r="G71" t="s" s="4">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H71" t="n" s="7">
         <v>0</v>
@@ -13502,21 +13501,21 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="10">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B72" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C72" t="s" s="4">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D72" t="s" s="4">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
       <c r="G72" t="s" s="4">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H72" t="n" s="7">
         <v>0</v>
@@ -13525,7 +13524,7 @@
         <v>0</v>
       </c>
       <c r="J72" t="s" s="4">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="K72" t="s" s="17">
         <v>53</v>
@@ -13536,21 +13535,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="10">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B73" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C73" t="s" s="4">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D73" t="s" s="4">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
       <c r="G73" t="s" s="4">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H73" t="n" s="7">
         <v>0</v>
@@ -13559,7 +13558,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="s" s="4">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="K73" t="s" s="17">
         <v>53</v>
@@ -13570,16 +13569,16 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="10">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B74" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C74" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="D74" t="s" s="4">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
@@ -13591,7 +13590,7 @@
         <v>0</v>
       </c>
       <c r="J74" t="s" s="4">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="K74" t="s" s="17">
         <v>53</v>
@@ -13602,16 +13601,16 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="10">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B75" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C75" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="D75" t="s" s="4">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
@@ -13623,7 +13622,7 @@
         <v>0</v>
       </c>
       <c r="J75" t="s" s="4">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="K75" t="s" s="17">
         <v>53</v>
@@ -13634,21 +13633,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="10">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B76" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C76" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="D76" t="s" s="4">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
       <c r="G76" t="s" s="4">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H76" t="n" s="7">
         <v>0</v>
@@ -13657,7 +13656,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="s" s="4">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="K76" t="s" s="17">
         <v>53</v>
@@ -13668,21 +13667,21 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="10">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B77" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C77" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="D77" t="s" s="4">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
       <c r="G77" t="s" s="4">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H77" t="n" s="7">
         <v>0</v>
@@ -13691,7 +13690,7 @@
         <v>0</v>
       </c>
       <c r="J77" t="s" s="4">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="K77" t="s" s="17">
         <v>53</v>
@@ -13702,16 +13701,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="10">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B78" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C78" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="D78" t="s" s="4">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
@@ -13723,7 +13722,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="s" s="4">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="K78" t="s" s="17">
         <v>53</v>
@@ -13734,21 +13733,21 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="10">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B79" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C79" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="D79" t="s" s="4">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
       <c r="G79" t="s" s="4">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H79" t="n" s="7">
         <v>0</v>
@@ -13757,7 +13756,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="s" s="4">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="K79" t="s" s="17">
         <v>53</v>
@@ -13768,21 +13767,21 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="10">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B80" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C80" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="D80" t="s" s="4">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
       <c r="G80" t="s" s="4">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="H80" t="n" s="7">
         <v>0</v>
@@ -13791,7 +13790,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="s" s="4">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="K80" t="s" s="17">
         <v>53</v>
@@ -13802,21 +13801,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="10">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B81" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C81" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="D81" t="s" s="4">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E81" s="5"/>
       <c r="F81" s="5"/>
       <c r="G81" t="s" s="4">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="H81" t="n" s="7">
         <v>0</v>
@@ -13825,7 +13824,7 @@
         <v>0</v>
       </c>
       <c r="J81" t="s" s="4">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="K81" t="s" s="17">
         <v>53</v>
@@ -13836,21 +13835,21 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="10">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B82" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C82" t="s" s="4">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="D82" t="s" s="4">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="E82" s="5"/>
       <c r="F82" s="5"/>
       <c r="G82" t="s" s="4">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="H82" t="n" s="7">
         <v>0</v>
@@ -13859,7 +13858,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="s" s="4">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="K82" t="s" s="17">
         <v>53</v>
@@ -13870,21 +13869,21 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="10">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B83" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C83" t="s" s="4">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="D83" t="s" s="4">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
       <c r="G83" t="s" s="4">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H83" t="n" s="7">
         <v>0</v>
@@ -13893,7 +13892,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="s" s="4">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="K83" t="s" s="17">
         <v>53</v>
@@ -13904,23 +13903,23 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="10">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B84" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C84" t="s" s="4">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="D84" t="s" s="4">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="E84" t="n" s="5">
         <v>2024</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" t="s" s="4">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="H84" t="n" s="7">
         <v>0</v>
@@ -13929,7 +13928,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="s" s="4">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="K84" t="s" s="17">
         <v>53</v>
@@ -13940,21 +13939,21 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="10">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B85" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C85" t="s" s="4">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="D85" t="s" s="4">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
       <c r="G85" t="s" s="4">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="H85" t="n" s="7">
         <v>0</v>
@@ -13963,7 +13962,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="s" s="4">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="K85" t="s" s="17">
         <v>53</v>
@@ -13974,15 +13973,17 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="10">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B86" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C86" t="s" s="4">
-        <v>273</v>
-      </c>
-      <c r="D86" s="4"/>
+        <v>269</v>
+      </c>
+      <c r="D86" t="s" s="4">
+        <v>305</v>
+      </c>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
       <c r="G86" s="4"/>
@@ -13993,7 +13994,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="s" s="4">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="K86" t="s" s="17">
         <v>53</v>
@@ -14004,21 +14005,21 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="10">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B87" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C87" t="s" s="4">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D87" t="s" s="4">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
       <c r="G87" t="s" s="4">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="H87" t="n" s="7">
         <v>0</v>
@@ -14027,7 +14028,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="s" s="4">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K87" t="s" s="17">
         <v>53</v>
@@ -14038,15 +14039,17 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="10">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B88" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C88" t="s" s="4">
-        <v>273</v>
-      </c>
-      <c r="D88" s="4"/>
+        <v>269</v>
+      </c>
+      <c r="D88" t="s" s="4">
+        <v>305</v>
+      </c>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
       <c r="G88" s="4"/>
@@ -14057,7 +14060,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="s" s="4">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="K88" t="s" s="17">
         <v>53</v>
@@ -14068,23 +14071,23 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="10">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B89" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C89" t="s" s="4">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="D89" t="s" s="4">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E89" t="n" s="5">
         <v>2025</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" t="s" s="4">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="H89" t="n" s="7">
         <v>0</v>
@@ -14093,7 +14096,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="s" s="4">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="K89" t="s" s="17">
         <v>53</v>
@@ -14104,15 +14107,17 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="10">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B90" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C90" t="s" s="4">
-        <v>260</v>
-      </c>
-      <c r="D90" s="4"/>
+        <v>257</v>
+      </c>
+      <c r="D90" t="s" s="4">
+        <v>266</v>
+      </c>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
       <c r="G90" s="4"/>
@@ -14123,7 +14128,7 @@
         <v>0</v>
       </c>
       <c r="J90" t="s" s="4">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="K90" t="s" s="17">
         <v>53</v>
@@ -14134,15 +14139,17 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="10">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B91" t="s" s="4">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C91" t="s" s="4">
-        <v>260</v>
-      </c>
-      <c r="D91" s="4"/>
+        <v>257</v>
+      </c>
+      <c r="D91" t="s" s="4">
+        <v>266</v>
+      </c>
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
       <c r="G91" s="4"/>
@@ -14153,7 +14160,7 @@
         <v>0</v>
       </c>
       <c r="J91" t="s" s="4">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="K91" t="s" s="17">
         <v>53</v>
@@ -14164,23 +14171,23 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="10">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B92" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C92" t="s" s="4">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D92" t="s" s="4">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E92" t="n" s="5">
         <v>2024</v>
       </c>
       <c r="F92" s="5"/>
       <c r="G92" t="s" s="4">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H92" t="n" s="7">
         <v>0</v>
@@ -14200,25 +14207,25 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="10">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B93" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C93" t="s" s="4">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D93" t="s" s="4">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E93" t="n" s="5">
         <v>2024</v>
       </c>
       <c r="F93" t="s" s="5">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G93" t="s" s="4">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H93" t="n" s="7">
         <v>0</v>
@@ -14238,23 +14245,23 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="10">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B94" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C94" t="s" s="4">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D94" t="s" s="4">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E94" t="n" s="5">
         <v>2024</v>
       </c>
       <c r="F94" s="5"/>
       <c r="G94" t="s" s="4">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H94" t="n" s="7">
         <v>0</v>
@@ -14274,23 +14281,23 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="10">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B95" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C95" t="s" s="4">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D95" t="s" s="4">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E95" t="n" s="5">
         <v>2025</v>
       </c>
       <c r="F95" s="5"/>
       <c r="G95" t="s" s="4">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H95" t="n" s="7">
         <v>0</v>
@@ -14310,25 +14317,25 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="10">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B96" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C96" t="s" s="4">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D96" t="s" s="4">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E96" t="n" s="5">
         <v>2026</v>
       </c>
       <c r="F96" t="s" s="5">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="G96" t="s" s="4">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H96" t="n" s="7">
         <v>0</v>
@@ -14348,25 +14355,25 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="10">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B97" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C97" t="s" s="4">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D97" t="s" s="4">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E97" t="n" s="5">
         <v>2027</v>
       </c>
       <c r="F97" t="s" s="5">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="G97" t="s" s="4">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H97" t="n" s="7">
         <v>0</v>
@@ -14386,16 +14393,16 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="10">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B98" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C98" t="s" s="4">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D98" t="s" s="4">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
@@ -14418,16 +14425,16 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="10">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B99" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C99" t="s" s="4">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D99" t="s" s="4">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
@@ -14450,16 +14457,16 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="10">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B100" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C100" t="s" s="4">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D100" t="s" s="4">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E100" s="5"/>
       <c r="F100" s="5"/>
@@ -14471,7 +14478,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="s" s="4">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="K100" t="s" s="17">
         <v>53</v>
@@ -14482,16 +14489,16 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="10">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B101" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C101" t="s" s="4">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D101" t="s" s="4">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E101" s="5"/>
       <c r="F101" t="n" s="5">
@@ -14505,7 +14512,7 @@
         <v>0</v>
       </c>
       <c r="J101" t="s" s="4">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K101" t="s" s="17">
         <v>53</v>
@@ -14516,16 +14523,16 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="10">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B102" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C102" t="s" s="4">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D102" t="s" s="4">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E102" s="5"/>
       <c r="F102" t="n" s="5">
@@ -14539,7 +14546,7 @@
         <v>0</v>
       </c>
       <c r="J102" t="s" s="4">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K102" t="s" s="17">
         <v>53</v>
@@ -14550,16 +14557,16 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="10">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B103" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C103" t="s" s="4">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D103" t="s" s="4">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E103" s="5"/>
       <c r="F103" t="n" s="5">
@@ -14573,7 +14580,7 @@
         <v>0</v>
       </c>
       <c r="J103" t="s" s="4">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K103" t="s" s="17">
         <v>53</v>
@@ -14584,16 +14591,16 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="10">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B104" t="s" s="4">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C104" t="s" s="4">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D104" t="s" s="4">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E104" s="5"/>
       <c r="F104" t="n" s="5">
@@ -14607,7 +14614,7 @@
         <v>0</v>
       </c>
       <c r="J104" t="s" s="4">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K104" t="s" s="17">
         <v>53</v>
@@ -14618,16 +14625,16 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="10">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B105" t="s" s="4">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C105" t="s" s="4">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D105" t="s" s="4">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E105" s="5"/>
       <c r="F105" s="5"/>
@@ -14650,16 +14657,16 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="10">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B106" t="s" s="4">
+        <v>346</v>
+      </c>
+      <c r="C106" t="s" s="4">
         <v>350</v>
       </c>
-      <c r="C106" t="s" s="4">
-        <v>354</v>
-      </c>
       <c r="D106" t="s" s="4">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E106" s="5"/>
       <c r="F106" s="5"/>
@@ -14671,7 +14678,7 @@
         <v>0</v>
       </c>
       <c r="J106" t="s" s="4">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K106" t="s" s="17">
         <v>53</v>
@@ -14682,21 +14689,21 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="10">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B107" t="s" s="4">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C107" t="s" s="4">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D107" t="s" s="4">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E107" s="5"/>
       <c r="F107" s="5"/>
       <c r="G107" t="s" s="4">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="H107" t="n" s="7">
         <v>0</v>
@@ -14716,15 +14723,15 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="10">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B108" t="s" s="4">
-        <v>350</v>
-      </c>
-      <c r="C108" t="s" s="4">
-        <v>359</v>
-      </c>
-      <c r="D108" s="4"/>
+        <v>346</v>
+      </c>
+      <c r="C108" s="4"/>
+      <c r="D108" t="s" s="4">
+        <v>355</v>
+      </c>
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
       <c r="G108" s="4"/>
@@ -14746,21 +14753,21 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="10">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B109" t="s" s="4">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C109" t="s" s="4">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D109" t="s" s="4">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E109" s="5"/>
       <c r="F109" s="5"/>
       <c r="G109" t="s" s="4">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="H109" t="n" s="7">
         <v>0</v>
@@ -14780,10 +14787,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="10">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B110" t="s" s="4">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
@@ -14797,7 +14804,7 @@
         <v>0</v>
       </c>
       <c r="J110" t="s" s="4">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K110" t="s" s="17">
         <v>53</v>
@@ -14808,25 +14815,25 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="10">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B111" t="s" s="4">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C111" t="s" s="4">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D111" t="s" s="4">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E111" t="n" s="5">
         <v>2024</v>
       </c>
       <c r="F111" t="s" s="5">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G111" t="s" s="4">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="H111" t="n" s="7">
         <v>0</v>
@@ -14846,15 +14853,17 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="10">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B112" t="s" s="4">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C112" t="s" s="4">
-        <v>373</v>
-      </c>
-      <c r="D112" s="4"/>
+        <v>369</v>
+      </c>
+      <c r="D112" t="s" s="4">
+        <v>370</v>
+      </c>
       <c r="E112" s="5"/>
       <c r="F112" s="5"/>
       <c r="G112" s="4"/>
@@ -14865,7 +14874,7 @@
         <v>0</v>
       </c>
       <c r="J112" t="s" s="4">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="K112" t="s" s="17">
         <v>53</v>
@@ -14876,20 +14885,20 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="10">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B113" t="s" s="4">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C113" t="s" s="4">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="D113" t="s" s="4">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E113" s="5"/>
       <c r="F113" t="s" s="5">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" t="n" s="7">
@@ -14899,7 +14908,7 @@
         <v>0</v>
       </c>
       <c r="J113" t="s" s="4">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="K113" t="s" s="17">
         <v>53</v>
@@ -14910,17 +14919,17 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="10">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B114" t="s" s="4">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
       <c r="G114" t="s" s="4">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="H114" t="n" s="7">
         <v>0</v>
@@ -14929,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="J114" t="s" s="4">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="K114" t="s" s="17">
         <v>53</v>
@@ -14940,14 +14949,14 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="10">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B115" t="s" s="4">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C115" s="4"/>
       <c r="D115" t="s" s="4">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E115" t="n" s="5">
         <v>2024</v>
@@ -14970,18 +14979,18 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="10">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B116" t="s" s="4">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C116" s="4"/>
       <c r="D116" t="s" s="4">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E116" s="5"/>
       <c r="F116" t="s" s="5">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" t="n" s="7">
@@ -15000,15 +15009,17 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="10">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B117" t="s" s="4">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C117" t="s" s="4">
-        <v>390</v>
-      </c>
-      <c r="D117" s="4"/>
+        <v>386</v>
+      </c>
+      <c r="D117" t="s" s="4">
+        <v>387</v>
+      </c>
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
       <c r="G117" s="4"/>
@@ -15041,7 +15052,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2">
@@ -15049,57 +15060,57 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="4">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="4">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="4">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="4">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="4">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="4">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>

--- a/database/Equipment_Register.xlsx
+++ b/database/Equipment_Register.xlsx
@@ -15,7 +15,7 @@
     <t xml:space="preserve">WORKSHOP EQUIPMENT REGISTER — 21 OCTOBER 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated 21/10/2026 12:07 by WMSv2 Recovery  •  116 assets  •  Availability = (operating hours − downtime) ÷ operating hours</t>
+    <t xml:space="preserve">Generated 21/10/2026 17:51 by WMSv2 Recovery  •  116 assets  •  Availability = (operating hours − downtime) ÷ operating hours</t>
   </si>
   <si>
     <t xml:space="preserve">ID</t>
@@ -222,7 +222,7 @@
     <t xml:space="preserve">Bucket Worn out</t>
   </si>
   <si>
-    <t xml:space="preserve">C-HV-EX 006</t>
+    <t xml:space="preserve">EX 006</t>
   </si>
   <si>
     <t xml:space="preserve">XE500</t>
@@ -369,7 +369,7 @@
     <t xml:space="preserve">Engine no start</t>
   </si>
   <si>
-    <t xml:space="preserve">C-HE-ADT 007</t>
+    <t xml:space="preserve">C-HEADT 007</t>
   </si>
   <si>
     <t xml:space="preserve">CAT00745P3F601164</t>
@@ -378,7 +378,7 @@
     <t xml:space="preserve">Differential problem</t>
   </si>
   <si>
-    <t xml:space="preserve">C-HE-ADT 008</t>
+    <t xml:space="preserve">C-HEADT 008</t>
   </si>
   <si>
     <t xml:space="preserve">CAT00745V3F601199</t>
@@ -1257,7 +1257,7 @@
     <t xml:space="preserve">  existing value.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Generated 21/10/2026 12:07.</t>
+    <t xml:space="preserve">• Generated 21/10/2026 17:51.</t>
   </si>
 </sst>
 </file>
